--- a/INCY.xlsx
+++ b/INCY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE6B17B-0FD0-4D63-A41D-079EB40BE895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FFD285-1AE4-457F-B4C8-AD56B4D62911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21195" yWindow="750" windowWidth="20670" windowHeight="19650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="19050" windowHeight="19840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="643">
   <si>
     <t>Name</t>
   </si>
@@ -2317,6 +2317,9 @@
   </si>
   <si>
     <t>MRGPRX2</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
@@ -3443,24 +3446,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:L67"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.26953125" style="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="11" width="7.453125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7265625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3486,10 +3489,10 @@
         <v>15</v>
       </c>
       <c r="K2" s="11">
-        <v>65.72</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="22" t="s">
         <v>373</v>
       </c>
@@ -3515,13 +3518,13 @@
         <v>16</v>
       </c>
       <c r="K3" s="19">
-        <v>192.598027</v>
+        <v>202.697746</v>
       </c>
       <c r="L3" s="52" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>482</v>
       </c>
@@ -3546,10 +3549,10 @@
       </c>
       <c r="K4" s="19">
         <f>K2*K3</f>
-        <v>12657.542334440001</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+        <v>24121.031773999999</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>456</v>
       </c>
@@ -3573,14 +3576,14 @@
         <v>17</v>
       </c>
       <c r="K5" s="19">
-        <f>987.293+462.207+69.875+29.668</f>
-        <v>1549.0429999999999</v>
+        <f>3982.375+104.387+553.365</f>
+        <v>4640.1270000000004</v>
       </c>
       <c r="L5" s="52" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>512</v>
       </c>
@@ -3607,10 +3610,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="52" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>521</v>
       </c>
@@ -3633,10 +3636,10 @@
       </c>
       <c r="K7" s="19">
         <f>K4-K5+K6</f>
-        <v>11108.499334440001</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+        <v>19480.904773999999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>522</v>
       </c>
@@ -3656,7 +3659,7 @@
       <c r="H8" s="67"/>
       <c r="K8" s="19"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>628</v>
       </c>
@@ -3679,7 +3682,7 @@
       <c r="K9" s="19"/>
       <c r="L9" s="30"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="56" t="s">
         <v>412</v>
       </c>
@@ -3703,7 +3706,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="11" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="56"/>
       <c r="C11" s="36"/>
       <c r="D11" s="4"/>
@@ -3717,7 +3720,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="12" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>494</v>
       </c>
@@ -3741,7 +3744,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="13" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
         <v>523</v>
       </c>
@@ -3765,7 +3768,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="14" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
         <v>525</v>
       </c>
@@ -3786,7 +3789,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="61" t="s">
         <v>618</v>
       </c>
@@ -3808,7 +3811,7 @@
       </c>
       <c r="J15" s="54"/>
     </row>
-    <row r="16" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="61" t="s">
         <v>532</v>
       </c>
@@ -3828,7 +3831,7 @@
       </c>
       <c r="J16" s="54"/>
     </row>
-    <row r="17" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
         <v>534</v>
       </c>
@@ -3850,7 +3853,7 @@
       </c>
       <c r="J17" s="54"/>
     </row>
-    <row r="18" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="61" t="s">
         <v>570</v>
       </c>
@@ -3872,7 +3875,7 @@
       <c r="H18" s="15"/>
       <c r="J18" s="54"/>
     </row>
-    <row r="19" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="61" t="s">
         <v>574</v>
       </c>
@@ -3892,7 +3895,7 @@
       <c r="H19" s="15"/>
       <c r="J19" s="54"/>
     </row>
-    <row r="20" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="61" t="s">
         <v>573</v>
       </c>
@@ -3912,7 +3915,7 @@
       <c r="H20" s="15"/>
       <c r="J20" s="54"/>
     </row>
-    <row r="21" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="61" t="s">
         <v>636</v>
       </c>
@@ -3930,7 +3933,7 @@
       <c r="H21" s="15"/>
       <c r="J21" s="54"/>
     </row>
-    <row r="22" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="61" t="s">
         <v>638</v>
       </c>
@@ -3948,7 +3951,7 @@
       <c r="H22" s="15"/>
       <c r="J22" s="54"/>
     </row>
-    <row r="23" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="61" t="s">
         <v>576</v>
       </c>
@@ -3968,7 +3971,7 @@
       <c r="H23" s="15"/>
       <c r="J23" s="54"/>
     </row>
-    <row r="24" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="61" t="s">
         <v>578</v>
       </c>
@@ -3984,7 +3987,7 @@
       <c r="H24" s="15"/>
       <c r="J24" s="54"/>
     </row>
-    <row r="25" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="61" t="s">
         <v>619</v>
       </c>
@@ -4004,7 +4007,7 @@
       <c r="H25" s="15"/>
       <c r="J25" s="54"/>
     </row>
-    <row r="26" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="61" t="s">
         <v>580</v>
       </c>
@@ -4020,7 +4023,7 @@
       <c r="H26" s="15"/>
       <c r="J26" s="54"/>
     </row>
-    <row r="27" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="61" t="s">
         <v>634</v>
       </c>
@@ -4036,7 +4039,7 @@
       <c r="H27" s="15"/>
       <c r="J27" s="54"/>
     </row>
-    <row r="28" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="61" t="s">
         <v>582</v>
       </c>
@@ -4052,7 +4055,7 @@
       <c r="H28" s="15"/>
       <c r="J28" s="54"/>
     </row>
-    <row r="29" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="61" t="s">
         <v>586</v>
       </c>
@@ -4070,7 +4073,7 @@
       <c r="H29" s="15"/>
       <c r="J29" s="54"/>
     </row>
-    <row r="30" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="61" t="s">
         <v>588</v>
       </c>
@@ -4088,7 +4091,7 @@
       <c r="H30" s="15"/>
       <c r="J30" s="54"/>
     </row>
-    <row r="31" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="61" t="s">
         <v>590</v>
       </c>
@@ -4106,7 +4109,7 @@
       <c r="H31" s="15"/>
       <c r="J31" s="54"/>
     </row>
-    <row r="32" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="61" t="s">
         <v>592</v>
       </c>
@@ -4124,7 +4127,7 @@
       <c r="H32" s="15"/>
       <c r="J32" s="54"/>
     </row>
-    <row r="33" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="61" t="s">
         <v>622</v>
       </c>
@@ -4142,7 +4145,7 @@
       <c r="H33" s="15"/>
       <c r="J33" s="54"/>
     </row>
-    <row r="34" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="61" t="s">
         <v>584</v>
       </c>
@@ -4160,7 +4163,7 @@
       <c r="H34" s="15"/>
       <c r="J34" s="54"/>
     </row>
-    <row r="35" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="56" t="s">
         <v>529</v>
       </c>
@@ -4177,8 +4180,8 @@
       <c r="G35" s="4"/>
       <c r="H35" s="18"/>
     </row>
-    <row r="36" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
       <c r="G37" s="54" t="s">
@@ -4186,7 +4189,7 @@
       </c>
       <c r="H37" s="13"/>
     </row>
-    <row r="38" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
       <c r="G38" s="54" t="s">
@@ -4194,7 +4197,7 @@
       </c>
       <c r="H38" s="13"/>
     </row>
-    <row r="39" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="G39" s="54" t="s">
@@ -4202,7 +4205,7 @@
       </c>
       <c r="H39" s="13"/>
     </row>
-    <row r="40" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="G40" s="54" t="s">
@@ -4213,7 +4216,7 @@
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
     </row>
-    <row r="41" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
       <c r="G41" s="54" t="s">
@@ -4224,7 +4227,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" ht="13" x14ac:dyDescent="0.3">
       <c r="B42" s="6"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -4235,7 +4238,7 @@
       </c>
       <c r="H42" s="13"/>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" ht="13" x14ac:dyDescent="0.3">
       <c r="B43" s="6"/>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -4246,7 +4249,7 @@
       </c>
       <c r="H43" s="13"/>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" ht="13" x14ac:dyDescent="0.3">
       <c r="B44" s="6"/>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -4257,7 +4260,7 @@
       </c>
       <c r="H44" s="13"/>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" ht="13" x14ac:dyDescent="0.3">
       <c r="B45" s="6"/>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -4268,7 +4271,7 @@
       </c>
       <c r="H45" s="13"/>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" ht="13" x14ac:dyDescent="0.3">
       <c r="B46" s="6"/>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -4279,7 +4282,7 @@
       </c>
       <c r="H46" s="13"/>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" ht="13" x14ac:dyDescent="0.3">
       <c r="B47" s="6"/>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -4290,7 +4293,7 @@
       </c>
       <c r="H47" s="13"/>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="12"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -4299,7 +4302,7 @@
       <c r="G48" s="12"/>
       <c r="H48" s="13"/>
     </row>
-    <row r="49" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
       <c r="E49" s="12"/>
@@ -4309,7 +4312,7 @@
       </c>
       <c r="H49" s="13"/>
     </row>
-    <row r="50" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="C50" s="13"/>
       <c r="D50" s="13"/>
       <c r="E50" s="12"/>
@@ -4319,7 +4322,7 @@
       </c>
       <c r="H50" s="13"/>
     </row>
-    <row r="51" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
       <c r="E51" s="12"/>
@@ -4329,7 +4332,7 @@
       </c>
       <c r="H51" s="13"/>
     </row>
-    <row r="52" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C52" s="13"/>
       <c r="D52" s="13"/>
       <c r="E52" s="12"/>
@@ -4339,7 +4342,7 @@
       </c>
       <c r="H52" s="13"/>
     </row>
-    <row r="53" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
       <c r="E53" s="12"/>
@@ -4349,7 +4352,7 @@
       </c>
       <c r="H53" s="13"/>
     </row>
-    <row r="54" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
       <c r="E54" s="12"/>
@@ -4359,67 +4362,67 @@
       </c>
       <c r="H54" s="13"/>
     </row>
-    <row r="55" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="G55" s="21" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="56" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="G56" s="21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="57" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="G57" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="58" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="G58" s="21" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="59" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="G59" s="21" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="60" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="G60" s="21" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="61" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="G61" s="21" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="62" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:8" ht="13" x14ac:dyDescent="0.3">
       <c r="G62" s="21" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="63" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:8" x14ac:dyDescent="0.25">
       <c r="G63" s="12" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="64" spans="3:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:8" x14ac:dyDescent="0.25">
       <c r="G64" s="12" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="65" spans="7:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G65" s="12" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="66" spans="7:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G66" s="12" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="67" spans="7:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G67" s="12" t="s">
         <v>247</v>
       </c>
@@ -4450,23 +4453,23 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161C603D-C783-4994-8723-E5E42ACA7B54}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="63" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>462</v>
       </c>
@@ -4474,7 +4477,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="63" t="s">
         <v>1</v>
       </c>
@@ -4482,7 +4485,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="63" t="s">
         <v>488</v>
       </c>
@@ -4490,7 +4493,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="63" t="s">
         <v>14</v>
       </c>
@@ -4498,32 +4501,32 @@
         <v>539</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="63" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C8" s="64" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C10" s="64" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C12" s="64" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C14" s="64" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C16" s="64" t="s">
         <v>563</v>
       </c>
@@ -4539,23 +4542,23 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4392F30C-4282-424F-90FD-2875BB463263}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="63" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>462</v>
       </c>
@@ -4563,7 +4566,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="63" t="s">
         <v>1</v>
       </c>
@@ -4571,7 +4574,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="63" t="s">
         <v>488</v>
       </c>
@@ -4579,32 +4582,32 @@
         <v>502</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="63" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C7" s="64" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C9" s="64" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C12" s="64" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C14" s="64" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C17" s="64" t="s">
         <v>556</v>
       </c>
@@ -4620,18 +4623,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D39AA32B-8BFC-49CA-8D2D-253905584093}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="63" t="s">
         <v>461</v>
       </c>
@@ -4639,12 +4642,12 @@
         <v>523</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="63" t="s">
         <v>1</v>
       </c>
@@ -4652,7 +4655,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="63" t="s">
         <v>488</v>
       </c>
@@ -4660,12 +4663,12 @@
         <v>609</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="63" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C7" s="64" t="s">
         <v>610</v>
       </c>
@@ -4681,18 +4684,18 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AFC9839-0F72-4CB9-8451-3654AA439C61}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="63" t="s">
         <v>461</v>
       </c>
@@ -4700,12 +4703,12 @@
         <v>529</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="63" t="s">
         <v>1</v>
       </c>
@@ -4713,7 +4716,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="63" t="s">
         <v>14</v>
       </c>
@@ -4721,7 +4724,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="63" t="s">
         <v>488</v>
       </c>
@@ -4729,12 +4732,12 @@
         <v>612</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="63" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C8" s="64" t="s">
         <v>613</v>
       </c>
@@ -4750,18 +4753,18 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{452E0AA5-7502-4061-A225-59AC76722896}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="63" t="s">
         <v>461</v>
       </c>
@@ -4769,12 +4772,12 @@
         <v>525</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="63" t="s">
         <v>1</v>
       </c>
@@ -4782,7 +4785,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="63" t="s">
         <v>488</v>
       </c>
@@ -4790,12 +4793,12 @@
         <v>526</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="63" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C7" s="64" t="s">
         <v>611</v>
       </c>
@@ -4811,23 +4814,23 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9653AC24-E69D-4DBB-9031-AF390FF5ED0E}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="63" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>462</v>
       </c>
@@ -4835,7 +4838,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="63" t="s">
         <v>1</v>
       </c>
@@ -4843,7 +4846,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="63" t="s">
         <v>488</v>
       </c>
@@ -4851,7 +4854,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="63" t="s">
         <v>14</v>
       </c>
@@ -4859,12 +4862,12 @@
         <v>615</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="63" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C8" s="64" t="s">
         <v>616</v>
       </c>
@@ -4880,20 +4883,20 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="75" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="75"/>
+    <col min="2" max="2" width="12.81640625" style="75" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="75"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="77" t="s">
         <v>52</v>
       </c>
       <c r="C1" s="78"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="75" t="s">
         <v>10</v>
       </c>
@@ -4901,7 +4904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="75" t="s">
         <v>1</v>
       </c>
@@ -4909,7 +4912,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="75" t="s">
         <v>11</v>
       </c>
@@ -4917,7 +4920,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="75" t="s">
         <v>22</v>
       </c>
@@ -4925,7 +4928,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="75" t="s">
         <v>14</v>
       </c>
@@ -4933,37 +4936,37 @@
         <v>321</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="75" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="78"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C8" s="78"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="75" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="78"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C10" s="76" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" s="78" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C12" s="79" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C13" s="78"/>
     </row>
   </sheetData>
@@ -4977,19 +4980,19 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>52</v>
       </c>
       <c r="C1" s="31"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>10</v>
       </c>
@@ -4997,7 +5000,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -5005,7 +5008,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -5013,7 +5016,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>22</v>
       </c>
@@ -5021,7 +5024,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>14</v>
       </c>
@@ -5029,32 +5032,32 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="31"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C8" s="31"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="31"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C10" s="64" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" s="31" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" s="31" t="s">
         <v>334</v>
       </c>
@@ -5070,14 +5073,14 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B2:C16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="75"/>
-    <col min="2" max="2" width="12.85546875" style="75" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="75"/>
+    <col min="1" max="1" width="9.1796875" style="75"/>
+    <col min="2" max="2" width="12.81640625" style="75" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="75"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="75" t="s">
         <v>10</v>
       </c>
@@ -5085,12 +5088,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="75" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="75" t="s">
         <v>1</v>
       </c>
@@ -5098,7 +5101,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="75" t="s">
         <v>11</v>
       </c>
@@ -5106,7 +5109,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="75" t="s">
         <v>22</v>
       </c>
@@ -5114,47 +5117,47 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="75" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="75" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="75" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="75" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="75" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C12" s="76" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C13" s="75" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C15" s="76" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C16" s="75" t="s">
         <v>50</v>
       </c>
@@ -5169,19 +5172,19 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="12.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
@@ -5189,12 +5192,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -5202,7 +5205,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -5210,12 +5213,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
@@ -5223,27 +5226,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C11" s="16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>44</v>
       </c>
@@ -5261,25 +5264,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:EC111"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="46" width="10.28515625" customWidth="1"/>
-    <col min="47" max="56" width="9.85546875" customWidth="1"/>
-    <col min="57" max="63" width="10.7109375" customWidth="1"/>
-    <col min="64" max="64" width="11.42578125" customWidth="1"/>
-    <col min="65" max="67" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="68" max="74" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" customWidth="1"/>
+    <col min="3" max="46" width="10.26953125" customWidth="1"/>
+    <col min="47" max="56" width="9.81640625" customWidth="1"/>
+    <col min="57" max="63" width="10.7265625" customWidth="1"/>
+    <col min="64" max="64" width="11.453125" customWidth="1"/>
+    <col min="65" max="67" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="68" max="74" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:88" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:88" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:88" x14ac:dyDescent="0.25">
       <c r="C2" s="40" t="s">
         <v>153</v>
       </c>
@@ -5540,7 +5543,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="3" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
       <c r="D3" s="28"/>
@@ -5612,7 +5615,7 @@
         <v>10149.999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="50" t="s">
         <v>448</v>
       </c>
@@ -5733,23 +5736,23 @@
         <v>337.86399999999998</v>
       </c>
       <c r="CC4" s="46">
-        <f>SUM(BG4:BJ4)</f>
+        <f t="shared" ref="CC4:CC9" si="1">SUM(BG4:BJ4)</f>
         <v>468.82169999999996</v>
       </c>
       <c r="CD4" s="46">
-        <f t="shared" ref="CD4:CG4" si="1">+CC4*1.2</f>
+        <f t="shared" ref="CD4:CG4" si="2">+CC4*1.2</f>
         <v>562.58603999999991</v>
       </c>
       <c r="CE4" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>675.10324799999989</v>
       </c>
       <c r="CF4" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>810.12389759999985</v>
       </c>
       <c r="CG4" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>972.14867711999977</v>
       </c>
       <c r="CH4" s="46">
@@ -5757,7 +5760,7 @@
         <v>194.42973542399997</v>
       </c>
     </row>
-    <row r="5" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="50" t="s">
         <v>447</v>
       </c>
@@ -5871,7 +5874,7 @@
       <c r="BY5" s="47"/>
       <c r="BZ5" s="47"/>
       <c r="CA5" s="46">
-        <f t="shared" ref="CA5:CA7" si="2">SUM(AY5:BB5)</f>
+        <f t="shared" ref="CA5:CA7" si="3">SUM(AY5:BB5)</f>
         <v>19.654</v>
       </c>
       <c r="CB5" s="46">
@@ -5879,31 +5882,31 @@
         <v>37.057000000000002</v>
       </c>
       <c r="CC5" s="46">
-        <f>SUM(BG5:BJ5)</f>
+        <f t="shared" si="1"/>
         <v>132.22199999999998</v>
       </c>
       <c r="CD5" s="47">
-        <f t="shared" ref="CD5:CH5" si="3">+CC5*1.15</f>
+        <f t="shared" ref="CD5:CH5" si="4">+CC5*1.15</f>
         <v>152.05529999999996</v>
       </c>
       <c r="CE5" s="47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>174.86359499999995</v>
       </c>
       <c r="CF5" s="47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>201.09313424999993</v>
       </c>
       <c r="CG5" s="47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>231.25710438749991</v>
       </c>
       <c r="CH5" s="47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>265.94567004562487</v>
       </c>
     </row>
-    <row r="6" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="50" t="s">
         <v>446</v>
       </c>
@@ -5964,7 +5967,7 @@
         <v>84000</v>
       </c>
       <c r="CA6" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>83.444999999999993</v>
       </c>
       <c r="CB6" s="46">
@@ -5972,7 +5975,7 @@
         <v>83.641999999999996</v>
       </c>
       <c r="CC6" s="46">
-        <f>SUM(BG6:BJ6)</f>
+        <f t="shared" si="1"/>
         <v>77.539999999999992</v>
       </c>
       <c r="CD6" s="46">
@@ -5980,23 +5983,23 @@
         <v>85.293999999999997</v>
       </c>
       <c r="CE6" s="46">
-        <f t="shared" ref="CE6:CH6" si="4">+CD6*0.99</f>
+        <f t="shared" ref="CE6:CH6" si="5">+CD6*0.99</f>
         <v>84.441059999999993</v>
       </c>
       <c r="CF6" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>83.59664939999999</v>
       </c>
       <c r="CG6" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>82.760682905999985</v>
       </c>
       <c r="CH6" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>81.933076076939983</v>
       </c>
     </row>
-    <row r="7" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="50" t="s">
         <v>520</v>
       </c>
@@ -6070,7 +6073,7 @@
       <c r="BY7" s="46"/>
       <c r="BZ7" s="46"/>
       <c r="CA7" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>105.83799999999999</v>
       </c>
       <c r="CB7" s="46">
@@ -6078,31 +6081,31 @@
         <v>111.62299999999999</v>
       </c>
       <c r="CC7" s="46">
-        <f>SUM(BG7:BJ7)</f>
+        <f t="shared" si="1"/>
         <v>112.056</v>
       </c>
       <c r="CD7" s="46">
-        <f t="shared" ref="CC7:CH7" si="5">+CC7*0.99</f>
+        <f t="shared" ref="CD7:CH7" si="6">+CC7*0.99</f>
         <v>110.93544</v>
       </c>
       <c r="CE7" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>109.8260856</v>
       </c>
       <c r="CF7" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>108.727824744</v>
       </c>
       <c r="CG7" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>107.64054649656001</v>
       </c>
       <c r="CH7" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>106.5641410315944</v>
       </c>
     </row>
-    <row r="8" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="50" t="s">
         <v>633</v>
       </c>
@@ -6142,7 +6145,7 @@
       <c r="CA8" s="46"/>
       <c r="CB8" s="46"/>
       <c r="CC8" s="46">
-        <f>SUM(BG8:BJ8)</f>
+        <f t="shared" si="1"/>
         <v>4.9529999999999994</v>
       </c>
       <c r="CD8" s="46"/>
@@ -6151,7 +6154,7 @@
       <c r="CG8" s="46"/>
       <c r="CH8" s="46"/>
     </row>
-    <row r="9" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="50" t="s">
         <v>337</v>
       </c>
@@ -6230,19 +6233,19 @@
         <v>2650.1475000000005</v>
       </c>
       <c r="CC9" s="46">
-        <f>SUM(BG9:BJ9)</f>
+        <f t="shared" si="1"/>
         <v>2622.50479</v>
       </c>
       <c r="CD9" s="46">
-        <f t="shared" ref="CC9:CF9" si="6">+CC9*1.1</f>
+        <f t="shared" ref="CD9:CF9" si="7">+CC9*1.1</f>
         <v>2884.7552690000002</v>
       </c>
       <c r="CE9" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3173.2307959000004</v>
       </c>
       <c r="CF9" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3490.5538754900008</v>
       </c>
       <c r="CG9" s="46">
@@ -6250,13 +6253,13 @@
         <v>698.1107750980002</v>
       </c>
       <c r="CH9" s="46">
-        <f t="shared" ref="CH9" si="7">+CG9*0.2</f>
+        <f t="shared" ref="CH9" si="8">+CG9*0.2</f>
         <v>139.62215501960006</v>
       </c>
       <c r="CI9" s="46"/>
       <c r="CJ9" s="46"/>
     </row>
-    <row r="10" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="50" t="s">
         <v>417</v>
       </c>
@@ -6310,71 +6313,71 @@
       <c r="AR10" s="28"/>
       <c r="AS10" s="28"/>
       <c r="AT10" s="28">
-        <f t="shared" ref="AT10" si="8">SUM(AT4:AT9)</f>
+        <f t="shared" ref="AT10" si="9">SUM(AT4:AT9)</f>
         <v>559.46699999999998</v>
       </c>
       <c r="AU10" s="28">
-        <f t="shared" ref="AU10" si="9">SUM(AU4:AU9)</f>
+        <f t="shared" ref="AU10" si="10">SUM(AU4:AU9)</f>
         <v>504.81099999999998</v>
       </c>
       <c r="AV10" s="28">
-        <f t="shared" ref="AV10" si="10">SUM(AV4:AV9)</f>
+        <f t="shared" ref="AV10" si="11">SUM(AV4:AV9)</f>
         <v>575.15</v>
       </c>
       <c r="AW10" s="28">
-        <f t="shared" ref="AW10" si="11">SUM(AW4:AW9)</f>
+        <f t="shared" ref="AW10" si="12">SUM(AW4:AW9)</f>
         <v>594.01300000000003</v>
       </c>
       <c r="AX10" s="28">
-        <f t="shared" ref="AX10" si="12">SUM(AX4:AX9)</f>
+        <f t="shared" ref="AX10" si="13">SUM(AX4:AX9)</f>
         <v>648.03800000000001</v>
       </c>
       <c r="AY10" s="28">
-        <f t="shared" ref="AY10" si="13">SUM(AY4:AY9)</f>
+        <f t="shared" ref="AY10" si="14">SUM(AY4:AY9)</f>
         <v>605.82100000000003</v>
       </c>
       <c r="AZ10" s="28">
-        <f t="shared" ref="AZ10" si="14">SUM(AZ4:AZ9)</f>
+        <f t="shared" ref="AZ10" si="15">SUM(AZ4:AZ9)</f>
         <v>663.851</v>
       </c>
       <c r="BA10" s="28">
-        <f t="shared" ref="BA10" si="15">SUM(BA4:BA9)</f>
+        <f t="shared" ref="BA10" si="16">SUM(BA4:BA9)</f>
         <v>713.01</v>
       </c>
       <c r="BB10" s="28">
-        <f t="shared" ref="BB10:BJ10" si="16">SUM(BB4:BB9)</f>
+        <f t="shared" ref="BB10:BJ10" si="17">SUM(BB4:BB9)</f>
         <v>764.21500000000003</v>
       </c>
       <c r="BC10" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>693.23700000000008</v>
       </c>
       <c r="BD10" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>827.005</v>
       </c>
       <c r="BE10" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>783.197</v>
       </c>
       <c r="BF10" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>861.72899999999993</v>
       </c>
       <c r="BG10" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>729.45600000000002</v>
       </c>
       <c r="BH10" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>906.56599999999992</v>
       </c>
       <c r="BI10" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>846.43132000000003</v>
       </c>
       <c r="BJ10" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>935.64416999999992</v>
       </c>
       <c r="BK10" s="28"/>
@@ -6383,15 +6386,15 @@
         <v>120000</v>
       </c>
       <c r="BR10" s="9">
-        <f t="shared" ref="BR10" si="17">SUM(BR4:BR9)</f>
+        <f t="shared" ref="BR10" si="18">SUM(BR4:BR9)</f>
         <v>0</v>
       </c>
       <c r="BS10" s="9">
-        <f t="shared" ref="BS10:BT10" si="18">SUM(BS4:BS9)</f>
+        <f t="shared" ref="BS10:BT10" si="19">SUM(BS4:BS9)</f>
         <v>0</v>
       </c>
       <c r="BT10" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="CA10" s="9">
@@ -6399,7 +6402,7 @@
         <v>2746.8970000000004</v>
       </c>
       <c r="CB10" s="9">
-        <f t="shared" ref="CB10:CH10" si="19">SUM(CB4:CB9)</f>
+        <f t="shared" ref="CB10:CH10" si="20">SUM(CB4:CB9)</f>
         <v>3220.3335000000006</v>
       </c>
       <c r="CC10" s="9">
@@ -6407,27 +6410,27 @@
         <v>3418.0974900000001</v>
       </c>
       <c r="CD10" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3795.626049</v>
       </c>
       <c r="CE10" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4217.4647845</v>
       </c>
       <c r="CF10" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4694.0953814840004</v>
       </c>
       <c r="CG10" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2091.9177860080599</v>
       </c>
       <c r="CH10" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>788.49477759775937</v>
       </c>
     </row>
-    <row r="11" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="50" t="s">
         <v>416</v>
       </c>
@@ -6549,14 +6552,14 @@
         <v>94706.44</v>
       </c>
       <c r="CA11" s="46">
-        <f t="shared" ref="CA11:CA16" si="20">SUM(AY11:BB11)</f>
+        <f t="shared" ref="CA11:CA16" si="21">SUM(AY11:BB11)</f>
         <v>5</v>
       </c>
       <c r="CB11" s="9">
         <v>0</v>
       </c>
       <c r="CC11" s="46">
-        <f>SUM(BG11:BJ11)</f>
+        <f t="shared" ref="CC11:CC16" si="22">SUM(BG11:BJ11)</f>
         <v>0</v>
       </c>
       <c r="CD11" s="9">
@@ -6575,7 +6578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="50" t="s">
         <v>449</v>
       </c>
@@ -6678,7 +6681,7 @@
       <c r="BK12" s="28"/>
       <c r="BL12" s="28"/>
       <c r="CA12" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>331.57500000000005</v>
       </c>
       <c r="CB12" s="9">
@@ -6686,19 +6689,19 @@
         <v>328.25925000000007</v>
       </c>
       <c r="CC12" s="46">
-        <f>SUM(BG12:BJ12)</f>
+        <f t="shared" si="22"/>
         <v>389.35499999999996</v>
       </c>
       <c r="CD12" s="9">
-        <f t="shared" ref="CC12:CF12" si="21">+CC12*0.99</f>
+        <f t="shared" ref="CD12:CF12" si="23">+CC12*0.99</f>
         <v>385.46144999999996</v>
       </c>
       <c r="CE12" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>381.60683549999993</v>
       </c>
       <c r="CF12" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>377.7907671449999</v>
       </c>
       <c r="CG12" s="9">
@@ -6706,11 +6709,11 @@
         <v>75.558153428999987</v>
       </c>
       <c r="CH12" s="9">
-        <f t="shared" ref="CH12:CH13" si="22">+CG12*0.2</f>
+        <f t="shared" ref="CH12:CH13" si="24">+CG12*0.2</f>
         <v>15.111630685799998</v>
       </c>
     </row>
-    <row r="13" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="50" t="s">
         <v>450</v>
       </c>
@@ -6813,7 +6816,7 @@
       <c r="BK13" s="28"/>
       <c r="BL13" s="28"/>
       <c r="CA13" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>134.547</v>
       </c>
       <c r="CB13" s="9">
@@ -6821,31 +6824,31 @@
         <v>133.20152999999999</v>
       </c>
       <c r="CC13" s="46">
-        <f>SUM(BG13:BJ13)</f>
+        <f t="shared" si="22"/>
         <v>132.26499999999999</v>
       </c>
       <c r="CD13" s="9">
-        <f t="shared" ref="CC13:CF13" si="23">+CC13*0.99</f>
+        <f t="shared" ref="CD13:CF13" si="25">+CC13*0.99</f>
         <v>130.94234999999998</v>
       </c>
       <c r="CE13" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>129.63292649999997</v>
       </c>
       <c r="CF13" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>128.33659723499997</v>
       </c>
       <c r="CG13" s="9">
-        <f t="shared" ref="CG13" si="24">+CF13*0.2</f>
+        <f t="shared" ref="CG13" si="26">+CF13*0.2</f>
         <v>25.667319446999997</v>
       </c>
       <c r="CH13" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>5.1334638893999998</v>
       </c>
     </row>
-    <row r="14" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="50" t="s">
         <v>451</v>
       </c>
@@ -6948,7 +6951,7 @@
       <c r="BK14" s="28"/>
       <c r="BL14" s="28"/>
       <c r="CA14" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15.411000000000001</v>
       </c>
       <c r="CB14" s="9">
@@ -6956,31 +6959,31 @@
         <v>15.411000000000001</v>
       </c>
       <c r="CC14" s="46">
-        <f>SUM(BG14:BJ14)</f>
+        <f t="shared" si="22"/>
         <v>21.128</v>
       </c>
       <c r="CD14" s="9">
-        <f t="shared" ref="CC14:CH14" si="25">+CC14</f>
+        <f t="shared" ref="CD14:CH14" si="27">+CC14</f>
         <v>21.128</v>
       </c>
       <c r="CE14" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21.128</v>
       </c>
       <c r="CF14" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21.128</v>
       </c>
       <c r="CG14" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21.128</v>
       </c>
       <c r="CH14" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21.128</v>
       </c>
     </row>
-    <row r="15" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="50" t="s">
         <v>627</v>
       </c>
@@ -7068,11 +7071,11 @@
       <c r="BL15" s="28"/>
       <c r="CA15" s="46"/>
       <c r="CC15" s="46">
-        <f>SUM(BG15:BJ15)</f>
+        <f t="shared" si="22"/>
         <v>3.1759999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="50" t="s">
         <v>415</v>
       </c>
@@ -7086,7 +7089,7 @@
         <v>135</v>
       </c>
       <c r="F16" s="28">
-        <f t="shared" ref="F16:F28" si="26">BO16-SUM(C16:E16)</f>
+        <f t="shared" ref="F16:F28" si="28">BO16-SUM(C16:E16)</f>
         <v>134</v>
       </c>
       <c r="G16" s="28">
@@ -7172,39 +7175,39 @@
         <v>495</v>
       </c>
       <c r="CA16" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="CB16" s="9">
-        <f t="shared" ref="CB16:CH16" si="27">+CA16</f>
+        <f t="shared" ref="CB16:CH16" si="29">+CA16</f>
         <v>0</v>
       </c>
       <c r="CC16" s="46">
-        <f>SUM(BG16:BJ16)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="CD16" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="CE16" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="CF16" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="CG16" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="CH16" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:133" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:133" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B17" s="10" t="s">
         <v>414</v>
       </c>
@@ -7213,83 +7216,83 @@
         <v>17288</v>
       </c>
       <c r="D17" s="10">
-        <f t="shared" ref="D17:L17" si="28">SUM(D10:D16)</f>
+        <f t="shared" ref="D17:L17" si="30">SUM(D10:D16)</f>
         <v>49847</v>
       </c>
       <c r="E17" s="10">
+        <f t="shared" si="30"/>
+        <v>16872</v>
+      </c>
+      <c r="F17" s="10">
         <f t="shared" si="28"/>
-        <v>16872</v>
-      </c>
-      <c r="F17" s="10">
-        <f t="shared" si="26"/>
         <v>85871</v>
       </c>
       <c r="G17" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>31973</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>16811</v>
       </c>
       <c r="I17" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>16782</v>
       </c>
       <c r="J17" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>28889</v>
       </c>
       <c r="K17" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>36179</v>
       </c>
       <c r="L17" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>86542</v>
       </c>
       <c r="AQ17" s="10">
-        <f t="shared" ref="AQ17:AT17" si="29">SUM(AQ10:AQ16)</f>
+        <f t="shared" ref="AQ17:AT17" si="31">SUM(AQ10:AQ16)</f>
         <v>0</v>
       </c>
       <c r="AR17" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AS17" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AT17" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>679.50900000000001</v>
       </c>
       <c r="AU17" s="10">
-        <f t="shared" ref="AU17:BA17" si="30">SUM(AU10:AU16)</f>
+        <f t="shared" ref="AU17:BA17" si="32">SUM(AU10:AU16)</f>
         <v>604.71800000000007</v>
       </c>
       <c r="AV17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>695.71199999999999</v>
       </c>
       <c r="AW17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>777.98699999999997</v>
       </c>
       <c r="AX17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>812.85300000000007</v>
       </c>
       <c r="AY17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>733.2349999999999</v>
       </c>
       <c r="AZ17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>781.39700000000005</v>
       </c>
       <c r="BA17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>823.303</v>
       </c>
       <c r="BB17" s="10">
@@ -7305,15 +7308,15 @@
         <v>954.61</v>
       </c>
       <c r="BE17" s="10">
-        <f t="shared" ref="BD17:BH17" si="31">SUM(BE10:BE16)</f>
+        <f t="shared" ref="BE17:BG17" si="33">SUM(BE10:BE16)</f>
         <v>914.02500000000009</v>
       </c>
       <c r="BF17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1011.3409999999999</v>
       </c>
       <c r="BG17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>855.42200000000014</v>
       </c>
       <c r="BH17" s="10">
@@ -7333,31 +7336,31 @@
         <v>3919</v>
       </c>
       <c r="BN17" s="10">
-        <f t="shared" ref="BN17:CE17" si="32">SUM(BN10:BN16)</f>
+        <f t="shared" ref="BN17:CE17" si="34">SUM(BN10:BN16)</f>
         <v>9265</v>
       </c>
       <c r="BO17" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>169878</v>
       </c>
       <c r="BP17" s="10">
-        <f t="shared" ref="BP17" si="33">SUM(BP10:BP16)</f>
+        <f t="shared" ref="BP17" si="35">SUM(BP10:BP16)</f>
         <v>92443</v>
       </c>
       <c r="BQ17" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>214706.44</v>
       </c>
       <c r="BR17" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BS17" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BT17" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="CA17" s="10">
@@ -7365,7 +7368,7 @@
         <v>3233.4300000000007</v>
       </c>
       <c r="CB17" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3697.2052800000006</v>
       </c>
       <c r="CC17" s="10">
@@ -7373,27 +7376,27 @@
         <v>3964.0214900000001</v>
       </c>
       <c r="CD17" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>4333.1578490000002</v>
       </c>
       <c r="CE17" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>4749.8325464999998</v>
       </c>
       <c r="CF17" s="10">
-        <f t="shared" ref="CF17:CH17" si="34">SUM(CF10:CF16)</f>
+        <f t="shared" ref="CF17:CH17" si="36">SUM(CF10:CF16)</f>
         <v>5221.3507458640006</v>
       </c>
       <c r="CG17" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>2214.27125888406</v>
       </c>
       <c r="CH17" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>829.86787217295944</v>
       </c>
     </row>
-    <row r="18" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="28" t="s">
         <v>181</v>
       </c>
@@ -7401,7 +7404,7 @@
       <c r="D18" s="28"/>
       <c r="E18" s="28"/>
       <c r="F18" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="G18" s="28"/>
@@ -7507,51 +7510,51 @@
         <v>10735.322</v>
       </c>
       <c r="BR18" s="9">
-        <f t="shared" ref="BR18:CE18" si="35">0.05*BR17</f>
+        <f t="shared" ref="BR18:CE18" si="37">0.05*BR17</f>
         <v>0</v>
       </c>
       <c r="BS18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BT18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="CA18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>161.67150000000004</v>
       </c>
       <c r="CB18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>184.86026400000003</v>
       </c>
       <c r="CC18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>198.2010745</v>
       </c>
       <c r="CD18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>216.65789245000002</v>
       </c>
       <c r="CE18" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>237.491627325</v>
       </c>
       <c r="CF18" s="9">
-        <f t="shared" ref="CF18" si="36">0.05*CF17</f>
+        <f t="shared" ref="CF18" si="38">0.05*CF17</f>
         <v>261.06753729320002</v>
       </c>
       <c r="CG18" s="9">
-        <f t="shared" ref="CG18" si="37">0.05*CG17</f>
+        <f t="shared" ref="CG18" si="39">0.05*CG17</f>
         <v>110.71356294420301</v>
       </c>
       <c r="CH18" s="9">
-        <f t="shared" ref="CH18" si="38">0.05*CH17</f>
+        <f t="shared" ref="CH18" si="40">0.05*CH17</f>
         <v>41.493393608647978</v>
       </c>
     </row>
-    <row r="19" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
         <v>262</v>
       </c>
@@ -7560,39 +7563,39 @@
         <v>17288</v>
       </c>
       <c r="D19" s="28">
-        <f t="shared" ref="D19:L19" si="39">D17-D18</f>
+        <f t="shared" ref="D19:L19" si="41">D17-D18</f>
         <v>49847</v>
       </c>
       <c r="E19" s="28">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>16872</v>
       </c>
       <c r="F19" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>85871</v>
       </c>
       <c r="G19" s="28">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>31973</v>
       </c>
       <c r="H19" s="28">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>16811</v>
       </c>
       <c r="I19" s="28">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>16782</v>
       </c>
       <c r="J19" s="28">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>28889</v>
       </c>
       <c r="K19" s="28">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>36168</v>
       </c>
       <c r="L19" s="28">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>86526</v>
       </c>
       <c r="M19" s="28"/>
@@ -7629,39 +7632,39 @@
       <c r="AR19" s="28"/>
       <c r="AS19" s="28"/>
       <c r="AT19" s="28">
-        <f t="shared" ref="AT19" si="40">+AT17-AT18</f>
+        <f t="shared" ref="AT19" si="42">+AT17-AT18</f>
         <v>648.81600000000003</v>
       </c>
       <c r="AU19" s="28">
-        <f t="shared" ref="AU19:BB19" si="41">+AU17-AU18</f>
+        <f t="shared" ref="AU19:BB19" si="43">+AU17-AU18</f>
         <v>581.12200000000007</v>
       </c>
       <c r="AV19" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>663.41</v>
       </c>
       <c r="AW19" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>744.02199999999993</v>
       </c>
       <c r="AX19" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>774.9670000000001</v>
       </c>
       <c r="AY19" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>696.61599999999987</v>
       </c>
       <c r="AZ19" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>736.822</v>
       </c>
       <c r="BA19" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>774.78200000000004</v>
       </c>
       <c r="BB19" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>843.67799999999988</v>
       </c>
       <c r="BC19" s="28">
@@ -7699,35 +7702,35 @@
       <c r="BK19" s="28"/>
       <c r="BL19" s="28"/>
       <c r="BM19" s="28">
-        <f t="shared" ref="BM19" si="42">BM17-BM18</f>
+        <f t="shared" ref="BM19" si="44">BM17-BM18</f>
         <v>3919</v>
       </c>
       <c r="BN19" s="28">
-        <f t="shared" ref="BN19" si="43">BN17-BN18</f>
+        <f t="shared" ref="BN19" si="45">BN17-BN18</f>
         <v>9265</v>
       </c>
       <c r="BO19" s="28">
-        <f t="shared" ref="BO19:BP19" si="44">BO17-BO18</f>
+        <f t="shared" ref="BO19:BP19" si="46">BO17-BO18</f>
         <v>169878</v>
       </c>
       <c r="BP19" s="28">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>92443</v>
       </c>
       <c r="BQ19" s="28">
-        <f t="shared" ref="BQ19" si="45">BQ17-BQ18</f>
+        <f t="shared" ref="BQ19" si="47">BQ17-BQ18</f>
         <v>203971.11800000002</v>
       </c>
       <c r="BR19" s="28">
-        <f t="shared" ref="BR19" si="46">BR17-BR18</f>
+        <f t="shared" ref="BR19" si="48">BR17-BR18</f>
         <v>0</v>
       </c>
       <c r="BS19" s="28">
-        <f t="shared" ref="BS19" si="47">BS17-BS18</f>
+        <f t="shared" ref="BS19" si="49">BS17-BS18</f>
         <v>0</v>
       </c>
       <c r="BT19" s="28">
-        <f t="shared" ref="BT19" si="48">BT17-BT18</f>
+        <f t="shared" ref="BT19" si="50">BT17-BT18</f>
         <v>0</v>
       </c>
       <c r="BU19" s="28"/>
@@ -7737,39 +7740,39 @@
       <c r="BY19" s="28"/>
       <c r="BZ19" s="28"/>
       <c r="CA19" s="28">
-        <f t="shared" ref="CA19:CE19" si="49">CA17-CA18</f>
+        <f t="shared" ref="CA19:CE19" si="51">CA17-CA18</f>
         <v>3071.7585000000008</v>
       </c>
       <c r="CB19" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>3512.3450160000007</v>
       </c>
       <c r="CC19" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>3765.8204155000003</v>
       </c>
       <c r="CD19" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>4116.4999565500002</v>
       </c>
       <c r="CE19" s="28">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>4512.3409191749997</v>
       </c>
       <c r="CF19" s="28">
-        <f t="shared" ref="CF19:CH19" si="50">CF17-CF18</f>
+        <f t="shared" ref="CF19:CH19" si="52">CF17-CF18</f>
         <v>4960.2832085708005</v>
       </c>
       <c r="CG19" s="28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2103.5576959398568</v>
       </c>
       <c r="CH19" s="28">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>788.3744785643114</v>
       </c>
     </row>
-    <row r="20" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
         <v>182</v>
       </c>
@@ -7783,7 +7786,7 @@
         <v>30609</v>
       </c>
       <c r="F20" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>32949</v>
       </c>
       <c r="G20" s="28">
@@ -7905,11 +7908,11 @@
         <v>75000</v>
       </c>
       <c r="CA20" s="46">
-        <f t="shared" ref="CA20:CA21" si="51">SUM(AY20:BB20)</f>
+        <f t="shared" ref="CA20:CA21" si="53">SUM(AY20:BB20)</f>
         <v>1499.1590000000001</v>
       </c>
     </row>
-    <row r="21" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
         <v>183</v>
       </c>
@@ -7923,7 +7926,7 @@
         <v>8458</v>
       </c>
       <c r="F21" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>10591</v>
       </c>
       <c r="G21" s="28">
@@ -8049,15 +8052,15 @@
         <v>59383.380000000005</v>
       </c>
       <c r="BR21" s="9">
-        <f t="shared" ref="BR21:BS21" si="52">BQ21*1.02</f>
+        <f t="shared" ref="BR21:BS21" si="54">BQ21*1.02</f>
         <v>60571.047600000005</v>
       </c>
       <c r="BS21" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>61782.468552000006</v>
       </c>
       <c r="CA21" s="46">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>947.94599999999991</v>
       </c>
       <c r="CB21" s="9">
@@ -8065,31 +8068,31 @@
         <v>758.35680000000002</v>
       </c>
       <c r="CC21" s="9">
-        <f t="shared" ref="CC21:CH21" si="53">+CB21*0.8</f>
+        <f t="shared" ref="CC21:CH21" si="55">+CB21*0.8</f>
         <v>606.68544000000009</v>
       </c>
       <c r="CD21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>485.34835200000009</v>
       </c>
       <c r="CE21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>388.27868160000008</v>
       </c>
       <c r="CF21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>310.62294528000007</v>
       </c>
       <c r="CG21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>248.49835622400008</v>
       </c>
       <c r="CH21" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>198.79868497920006</v>
       </c>
     </row>
-    <row r="22" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
         <v>261</v>
       </c>
@@ -8103,7 +8106,7 @@
         <v>-139</v>
       </c>
       <c r="F22" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>20</v>
       </c>
       <c r="G22" s="28">
@@ -8183,7 +8186,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="23" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="50" t="s">
         <v>418</v>
       </c>
@@ -8192,39 +8195,39 @@
         <v>37118</v>
       </c>
       <c r="D23" s="28">
-        <f t="shared" ref="D23:I23" si="54">SUM(D20:D22)</f>
+        <f t="shared" ref="D23:I23" si="56">SUM(D20:D22)</f>
         <v>36223</v>
       </c>
       <c r="E23" s="28">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>38928</v>
       </c>
       <c r="F23" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>43560</v>
       </c>
       <c r="G23" s="28">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>47798</v>
       </c>
       <c r="H23" s="28">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>57925</v>
       </c>
       <c r="I23" s="28">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>58886</v>
       </c>
       <c r="J23" s="28">
-        <f t="shared" ref="J23:L23" si="55">SUM(J20:J22)</f>
+        <f t="shared" ref="J23:L23" si="57">SUM(J20:J22)</f>
         <v>73029</v>
       </c>
       <c r="K23" s="28">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>70356</v>
       </c>
       <c r="L23" s="28">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>71307</v>
       </c>
       <c r="M23" s="28"/>
@@ -8261,7 +8264,7 @@
       <c r="AR23" s="28"/>
       <c r="AS23" s="28"/>
       <c r="AT23" s="28">
-        <f t="shared" ref="AT23" si="56">+AT21+AT20</f>
+        <f t="shared" ref="AT23" si="58">+AT21+AT20</f>
         <v>527.91800000000001</v>
       </c>
       <c r="AU23" s="28">
@@ -8301,19 +8304,19 @@
         <v>669.63699999999994</v>
       </c>
       <c r="BD23" s="28">
-        <f t="shared" ref="BD23:BH23" si="57">+BD20+BD21</f>
+        <f t="shared" ref="BD23:BG23" si="59">+BD20+BD21</f>
         <v>630.95100000000002</v>
       </c>
       <c r="BE23" s="28">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>590.76400000000001</v>
       </c>
       <c r="BF23" s="28">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>679.16100000000006</v>
       </c>
       <c r="BG23" s="28">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>665.77199999999993</v>
       </c>
       <c r="BH23" s="28">
@@ -8331,35 +8334,35 @@
       <c r="BK23" s="28"/>
       <c r="BL23" s="28"/>
       <c r="BM23" s="28">
-        <f t="shared" ref="BM23" si="58">SUM(BM20:BM22)</f>
+        <f t="shared" ref="BM23" si="60">SUM(BM20:BM22)</f>
         <v>163208</v>
       </c>
       <c r="BN23" s="28">
-        <f t="shared" ref="BN23" si="59">SUM(BN20:BN22)</f>
+        <f t="shared" ref="BN23" si="61">SUM(BN20:BN22)</f>
         <v>149033</v>
       </c>
       <c r="BO23" s="28">
-        <f t="shared" ref="BO23:BP23" si="60">SUM(BO20:BO22)</f>
+        <f t="shared" ref="BO23:BP23" si="62">SUM(BO20:BO22)</f>
         <v>155829</v>
       </c>
       <c r="BP23" s="28">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>237638</v>
       </c>
       <c r="BQ23" s="28">
-        <f t="shared" ref="BQ23" si="61">SUM(BQ20:BQ22)</f>
+        <f t="shared" ref="BQ23" si="63">SUM(BQ20:BQ22)</f>
         <v>159383.38</v>
       </c>
       <c r="BR23" s="28">
-        <f t="shared" ref="BR23" si="62">SUM(BR20:BR22)</f>
+        <f t="shared" ref="BR23" si="64">SUM(BR20:BR22)</f>
         <v>135571.04759999999</v>
       </c>
       <c r="BS23" s="28">
-        <f t="shared" ref="BS23:CE23" si="63">SUM(BS20:BS22)</f>
+        <f t="shared" ref="BS23:CE23" si="65">SUM(BS20:BS22)</f>
         <v>61782.468552000006</v>
       </c>
       <c r="BT23" s="28">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="BU23" s="28"/>
@@ -8373,35 +8376,35 @@
         <v>2447.105</v>
       </c>
       <c r="CB23" s="28">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>758.35680000000002</v>
       </c>
       <c r="CC23" s="28">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>606.68544000000009</v>
       </c>
       <c r="CD23" s="28">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>485.34835200000009</v>
       </c>
       <c r="CE23" s="28">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>388.27868160000008</v>
       </c>
       <c r="CF23" s="28">
-        <f t="shared" ref="CF23:CH23" si="64">SUM(CF20:CF22)</f>
+        <f t="shared" ref="CF23:CH23" si="66">SUM(CF20:CF22)</f>
         <v>310.62294528000007</v>
       </c>
       <c r="CG23" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>248.49835622400008</v>
       </c>
       <c r="CH23" s="28">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>198.79868497920006</v>
       </c>
     </row>
-    <row r="24" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="50" t="s">
         <v>146</v>
       </c>
@@ -8410,39 +8413,39 @@
         <v>-19830</v>
       </c>
       <c r="D24" s="28">
-        <f t="shared" ref="D24:I24" si="65">D19-D23</f>
+        <f t="shared" ref="D24:I24" si="67">D19-D23</f>
         <v>13624</v>
       </c>
       <c r="E24" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>-22056</v>
       </c>
       <c r="F24" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>42311</v>
       </c>
       <c r="G24" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>-15825</v>
       </c>
       <c r="H24" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>-41114</v>
       </c>
       <c r="I24" s="28">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>-42104</v>
       </c>
       <c r="J24" s="28">
-        <f t="shared" ref="J24:L24" si="66">J19-J23</f>
+        <f t="shared" ref="J24:L24" si="68">J19-J23</f>
         <v>-44140</v>
       </c>
       <c r="K24" s="28">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>-34188</v>
       </c>
       <c r="L24" s="28">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>15219</v>
       </c>
       <c r="M24" s="28"/>
@@ -8479,39 +8482,39 @@
       <c r="AR24" s="28"/>
       <c r="AS24" s="28"/>
       <c r="AT24" s="28">
-        <f t="shared" ref="AT24" si="67">+AT19-AT23</f>
+        <f t="shared" ref="AT24" si="69">+AT19-AT23</f>
         <v>120.89800000000002</v>
       </c>
       <c r="AU24" s="28">
-        <f t="shared" ref="AU24:BB24" si="68">+AU19-AU23</f>
+        <f t="shared" ref="AU24:BB24" si="70">+AU19-AU23</f>
         <v>180.78700000000009</v>
       </c>
       <c r="AV24" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>195.41399999999999</v>
       </c>
       <c r="AW24" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>100.40199999999993</v>
       </c>
       <c r="AX24" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>123.55600000000015</v>
       </c>
       <c r="AY24" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>176.8889999999999</v>
       </c>
       <c r="AZ24" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>182.16800000000001</v>
       </c>
       <c r="BA24" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>124.31500000000005</v>
       </c>
       <c r="BB24" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>121.42099999999982</v>
       </c>
       <c r="BC24" s="28">
@@ -8519,19 +8522,19 @@
         <v>88.367000000000189</v>
       </c>
       <c r="BD24" s="28">
-        <f t="shared" ref="BD24:BG24" si="69">+BD19-BD23</f>
+        <f t="shared" ref="BD24:BG24" si="71">+BD19-BD23</f>
         <v>261.50900000000001</v>
       </c>
       <c r="BE24" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>269.34700000000009</v>
       </c>
       <c r="BF24" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>268.60499999999979</v>
       </c>
       <c r="BG24" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>134.69100000000026</v>
       </c>
       <c r="BH24" s="28">
@@ -8549,35 +8552,35 @@
       <c r="BK24" s="28"/>
       <c r="BL24" s="28"/>
       <c r="BM24" s="28">
-        <f t="shared" ref="BM24" si="70">BM19-BM23</f>
+        <f t="shared" ref="BM24" si="72">BM19-BM23</f>
         <v>-159289</v>
       </c>
       <c r="BN24" s="28">
-        <f t="shared" ref="BN24" si="71">BN19-BN23</f>
+        <f t="shared" ref="BN24" si="73">BN19-BN23</f>
         <v>-139768</v>
       </c>
       <c r="BO24" s="28">
-        <f t="shared" ref="BO24:BP24" si="72">BO19-BO23</f>
+        <f t="shared" ref="BO24:BP24" si="74">BO19-BO23</f>
         <v>14049</v>
       </c>
       <c r="BP24" s="28">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>-145195</v>
       </c>
       <c r="BQ24" s="28">
-        <f t="shared" ref="BQ24" si="73">BQ19-BQ23</f>
+        <f t="shared" ref="BQ24" si="75">BQ19-BQ23</f>
         <v>44587.738000000012</v>
       </c>
       <c r="BR24" s="28">
-        <f t="shared" ref="BR24" si="74">BR19-BR23</f>
+        <f t="shared" ref="BR24" si="76">BR19-BR23</f>
         <v>-135571.04759999999</v>
       </c>
       <c r="BS24" s="28">
-        <f t="shared" ref="BS24:BT24" si="75">BS19-BS23</f>
+        <f t="shared" ref="BS24:BT24" si="77">BS19-BS23</f>
         <v>-61782.468552000006</v>
       </c>
       <c r="BT24" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="BU24" s="28"/>
@@ -8587,39 +8590,39 @@
       <c r="BY24" s="28"/>
       <c r="BZ24" s="28"/>
       <c r="CA24" s="28">
-        <f t="shared" ref="CA24:CH24" si="76">CA19-CA23</f>
+        <f t="shared" ref="CA24:CH24" si="78">CA19-CA23</f>
         <v>624.6535000000008</v>
       </c>
       <c r="CB24" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>2753.9882160000006</v>
       </c>
       <c r="CC24" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>3159.1349755000001</v>
       </c>
       <c r="CD24" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>3631.1516045500002</v>
       </c>
       <c r="CE24" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>4124.0622375749999</v>
       </c>
       <c r="CF24" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>4649.6602632908007</v>
       </c>
       <c r="CG24" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>1855.0593397158568</v>
       </c>
       <c r="CH24" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>589.57579358511134</v>
       </c>
     </row>
-    <row r="25" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
         <v>263</v>
       </c>
@@ -8636,7 +8639,7 @@
         <v>-10303</v>
       </c>
       <c r="F25" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-9771</v>
       </c>
       <c r="G25" s="28">
@@ -8781,7 +8784,7 @@
         <v>-42000</v>
       </c>
     </row>
-    <row r="26" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="28" t="s">
         <v>264</v>
       </c>
@@ -8798,7 +8801,7 @@
         <v>-32359</v>
       </c>
       <c r="F26" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>32540</v>
       </c>
       <c r="G26" s="28">
@@ -8818,11 +8821,11 @@
         <v>-55080</v>
       </c>
       <c r="K26" s="28">
-        <f t="shared" ref="K26:L26" si="77">SUM(K24:K25)</f>
+        <f t="shared" ref="K26:L26" si="79">SUM(K24:K25)</f>
         <v>-45426</v>
       </c>
       <c r="L26" s="28">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>4104</v>
       </c>
       <c r="M26" s="28"/>
@@ -8859,105 +8862,105 @@
       <c r="AR26" s="28"/>
       <c r="AS26" s="28"/>
       <c r="AT26" s="28">
-        <f t="shared" ref="AT26" si="78">+AT24+AT25</f>
+        <f t="shared" ref="AT26" si="80">+AT24+AT25</f>
         <v>112.85100000000003</v>
       </c>
       <c r="AU26" s="28">
-        <f t="shared" ref="AU26:BC26" si="79">+AU24+AU25</f>
+        <f t="shared" ref="AU26:BC26" si="81">+AU24+AU25</f>
         <v>179.0210000000001</v>
       </c>
       <c r="AV26" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>189.60299999999998</v>
       </c>
       <c r="AW26" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>92.761999999999929</v>
       </c>
       <c r="AX26" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>120.97700000000016</v>
       </c>
       <c r="AY26" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>177.46899999999991</v>
       </c>
       <c r="AZ26" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>179.46800000000002</v>
       </c>
       <c r="BA26" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>133.41800000000006</v>
       </c>
       <c r="BB26" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>147.39099999999982</v>
       </c>
       <c r="BC26" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>120.77100000000019</v>
       </c>
       <c r="BD26" s="28">
-        <f t="shared" ref="BD26" si="80">+BD24+BD25</f>
+        <f t="shared" ref="BD26" si="82">+BD24+BD25</f>
         <v>304.17700000000002</v>
       </c>
       <c r="BE26" s="28">
-        <f t="shared" ref="BE26" si="81">+BE24+BE25</f>
+        <f t="shared" ref="BE26" si="83">+BE24+BE25</f>
         <v>315.71800000000007</v>
       </c>
       <c r="BF26" s="28">
-        <f t="shared" ref="BF26:BJ26" si="82">+BF24+BF25</f>
+        <f t="shared" ref="BF26:BJ26" si="84">+BF24+BF25</f>
         <v>319.04099999999977</v>
       </c>
       <c r="BG26" s="28">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>179.43500000000026</v>
       </c>
       <c r="BH26" s="28">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>-329.03200000000004</v>
       </c>
       <c r="BI26" s="28">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>668.3613276000001</v>
       </c>
       <c r="BJ26" s="28">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>739.3713280999998</v>
       </c>
       <c r="BK26" s="28"/>
       <c r="BL26" s="28"/>
       <c r="BM26" s="28">
-        <f t="shared" ref="BM26:BS26" si="83">SUM(BM24:BM25)</f>
+        <f t="shared" ref="BM26:BS26" si="85">SUM(BM24:BM25)</f>
         <v>-178920</v>
       </c>
       <c r="BN26" s="28">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>-171843</v>
       </c>
       <c r="BO26" s="28">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>-27858</v>
       </c>
       <c r="BP26" s="28">
-        <f t="shared" ref="BP26" si="84">SUM(BP24:BP25)</f>
+        <f t="shared" ref="BP26" si="86">SUM(BP24:BP25)</f>
         <v>-188552</v>
       </c>
       <c r="BQ26" s="28">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>2587.7380000000121</v>
       </c>
       <c r="BR26" s="28">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>-177571.04759999999</v>
       </c>
       <c r="BS26" s="28">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>-103782.46855200001</v>
       </c>
       <c r="BT26" s="28">
-        <f t="shared" ref="BT26:CE26" si="85">SUM(BT24:BT25)</f>
+        <f t="shared" ref="BT26:CE26" si="87">SUM(BT24:BT25)</f>
         <v>0</v>
       </c>
       <c r="BU26" s="28"/>
@@ -8967,39 +8970,39 @@
       <c r="BY26" s="28"/>
       <c r="BZ26" s="28"/>
       <c r="CA26" s="28">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>624.6535000000008</v>
       </c>
       <c r="CB26" s="28">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>2753.9882160000006</v>
       </c>
       <c r="CC26" s="28">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>3159.1349755000001</v>
       </c>
       <c r="CD26" s="28">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>3631.1516045500002</v>
       </c>
       <c r="CE26" s="28">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>4124.0622375749999</v>
       </c>
       <c r="CF26" s="28">
-        <f t="shared" ref="CF26:CH26" si="86">SUM(CF24:CF25)</f>
+        <f t="shared" ref="CF26:CH26" si="88">SUM(CF24:CF25)</f>
         <v>4649.6602632908007</v>
       </c>
       <c r="CG26" s="28">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>1855.0593397158568</v>
       </c>
       <c r="CH26" s="28">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>589.57579358511134</v>
       </c>
     </row>
-    <row r="27" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="28" t="s">
         <v>265</v>
       </c>
@@ -9011,7 +9014,7 @@
         <v>658</v>
       </c>
       <c r="F27" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-989</v>
       </c>
       <c r="G27" s="28"/>
@@ -9127,35 +9130,35 @@
         <v>124.93070000000017</v>
       </c>
       <c r="CB27" s="28">
-        <f t="shared" ref="CB27:CH27" si="87">+CB26*0.2</f>
+        <f t="shared" ref="CB27:CH27" si="89">+CB26*0.2</f>
         <v>550.79764320000015</v>
       </c>
       <c r="CC27" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>631.82699510000009</v>
       </c>
       <c r="CD27" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>726.23032091000005</v>
       </c>
       <c r="CE27" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>824.81244751500003</v>
       </c>
       <c r="CF27" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>929.93205265816016</v>
       </c>
       <c r="CG27" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>371.01186794317141</v>
       </c>
       <c r="CH27" s="28">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>117.91515871702228</v>
       </c>
     </row>
-    <row r="28" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="28" t="s">
         <v>266</v>
       </c>
@@ -9164,39 +9167,39 @@
         <v>-31414</v>
       </c>
       <c r="D28" s="28">
-        <f t="shared" ref="D28:I28" si="88">D26+D27</f>
+        <f t="shared" ref="D28:I28" si="90">D26+D27</f>
         <v>3706</v>
       </c>
       <c r="E28" s="28">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>-31701</v>
       </c>
       <c r="F28" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>31551</v>
       </c>
       <c r="G28" s="28">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>-26512</v>
       </c>
       <c r="H28" s="28">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>-51870</v>
       </c>
       <c r="I28" s="28">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>-53078</v>
       </c>
       <c r="J28" s="28">
-        <f t="shared" ref="J28:L28" si="89">J26+J27</f>
+        <f t="shared" ref="J28:L28" si="91">J26+J27</f>
         <v>-55080</v>
       </c>
       <c r="K28" s="28">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>-45426</v>
       </c>
       <c r="L28" s="28">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>4104</v>
       </c>
       <c r="M28" s="28"/>
@@ -9233,105 +9236,105 @@
       <c r="AR28" s="28"/>
       <c r="AS28" s="28"/>
       <c r="AT28" s="28">
-        <f t="shared" ref="AT28" si="90">+AT26-AT27</f>
+        <f t="shared" ref="AT28" si="92">+AT26-AT27</f>
         <v>94.599000000000032</v>
       </c>
       <c r="AU28" s="28">
-        <f t="shared" ref="AU28:BC28" si="91">+AU26-AU27</f>
+        <f t="shared" ref="AU28:BC28" si="93">+AU26-AU27</f>
         <v>163.23400000000009</v>
       </c>
       <c r="AV28" s="28">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>167.42599999999999</v>
       </c>
       <c r="AW28" s="28">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>65.031999999999925</v>
       </c>
       <c r="AX28" s="28">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>120.97700000000016</v>
       </c>
       <c r="AY28" s="28">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>144.9259999999999</v>
       </c>
       <c r="AZ28" s="28">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>111.52200000000002</v>
       </c>
       <c r="BA28" s="28">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>97.605000000000061</v>
       </c>
       <c r="BB28" s="28">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>95.236999999999824</v>
       </c>
       <c r="BC28" s="28">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>90.618000000000194</v>
       </c>
       <c r="BD28" s="28">
-        <f t="shared" ref="BD28" si="92">+BD26-BD27</f>
+        <f t="shared" ref="BD28" si="94">+BD26-BD27</f>
         <v>230.12100000000004</v>
       </c>
       <c r="BE28" s="28">
-        <f t="shared" ref="BE28" si="93">+BE26-BE27</f>
+        <f t="shared" ref="BE28" si="95">+BE26-BE27</f>
         <v>253.18800000000007</v>
       </c>
       <c r="BF28" s="28">
-        <f t="shared" ref="BF28:BJ28" si="94">+BF26-BF27</f>
+        <f t="shared" ref="BF28:BJ28" si="96">+BF26-BF27</f>
         <v>249.16399999999976</v>
       </c>
       <c r="BG28" s="28">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>112.82400000000025</v>
       </c>
       <c r="BH28" s="28">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>-383.85600000000005</v>
       </c>
       <c r="BI28" s="28">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>601.52519484000004</v>
       </c>
       <c r="BJ28" s="28">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>665.43419528999982</v>
       </c>
       <c r="BK28" s="28"/>
       <c r="BL28" s="28"/>
       <c r="BM28" s="28">
-        <f t="shared" ref="BM28" si="95">BM26+BM27</f>
+        <f t="shared" ref="BM28" si="97">BM26+BM27</f>
         <v>-178920</v>
       </c>
       <c r="BN28" s="28">
-        <f t="shared" ref="BN28" si="96">BN26+BN27</f>
+        <f t="shared" ref="BN28" si="98">BN26+BN27</f>
         <v>-171843</v>
       </c>
       <c r="BO28" s="28">
-        <f t="shared" ref="BO28:BP28" si="97">BO26+BO27</f>
+        <f t="shared" ref="BO28:BP28" si="99">BO26+BO27</f>
         <v>-27858</v>
       </c>
       <c r="BP28" s="28">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>-188552</v>
       </c>
       <c r="BQ28" s="28">
-        <f t="shared" ref="BQ28" si="98">BQ26+BQ27</f>
+        <f t="shared" ref="BQ28" si="100">BQ26+BQ27</f>
         <v>2587.7380000000121</v>
       </c>
       <c r="BR28" s="28">
-        <f t="shared" ref="BR28" si="99">BR26+BR27</f>
+        <f t="shared" ref="BR28" si="101">BR26+BR27</f>
         <v>-177571.04759999999</v>
       </c>
       <c r="BS28" s="28">
-        <f t="shared" ref="BS28:BT28" si="100">BS26+BS27</f>
+        <f t="shared" ref="BS28:BT28" si="102">BS26+BS27</f>
         <v>-103782.46855200001</v>
       </c>
       <c r="BT28" s="28">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="BU28" s="28"/>
@@ -9345,31 +9348,31 @@
         <v>499.72280000000063</v>
       </c>
       <c r="CB28" s="28">
-        <f t="shared" ref="CB28:CH28" si="101">+CB26-CB27</f>
+        <f t="shared" ref="CB28:CH28" si="103">+CB26-CB27</f>
         <v>2203.1905728000006</v>
       </c>
       <c r="CC28" s="28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>2527.3079803999999</v>
       </c>
       <c r="CD28" s="28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>2904.9212836400002</v>
       </c>
       <c r="CE28" s="28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>3299.2497900600001</v>
       </c>
       <c r="CF28" s="28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>3719.7282106326406</v>
       </c>
       <c r="CG28" s="28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1484.0474717726854</v>
       </c>
       <c r="CH28" s="28">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>471.66063486808906</v>
       </c>
       <c r="CI28" s="9">
@@ -9377,191 +9380,191 @@
         <v>448.07760312468457</v>
       </c>
       <c r="CJ28" s="9">
-        <f t="shared" ref="CJ28:EC28" si="102">CI28*(1+$CL$33)</f>
+        <f t="shared" ref="CJ28:EC28" si="104">CI28*(1+$CL$33)</f>
         <v>425.67372296845031</v>
       </c>
       <c r="CK28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>404.39003682002777</v>
       </c>
       <c r="CL28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>384.17053497902634</v>
       </c>
       <c r="CM28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>364.96200823007501</v>
       </c>
       <c r="CN28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>346.71390781857127</v>
       </c>
       <c r="CO28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>329.37821242764267</v>
       </c>
       <c r="CP28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>312.90930180626054</v>
       </c>
       <c r="CQ28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>297.26383671594749</v>
       </c>
       <c r="CR28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>282.40064488015008</v>
       </c>
       <c r="CS28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>268.28061263614256</v>
       </c>
       <c r="CT28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>254.86658200433541</v>
       </c>
       <c r="CU28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>242.12325290411863</v>
       </c>
       <c r="CV28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>230.01709025891267</v>
       </c>
       <c r="CW28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>218.51623574596704</v>
       </c>
       <c r="CX28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>207.59042395866868</v>
       </c>
       <c r="CY28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>197.21090276073522</v>
       </c>
       <c r="CZ28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>187.35035762269845</v>
       </c>
       <c r="DA28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>177.98283974156351</v>
       </c>
       <c r="DB28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>169.08369775448531</v>
       </c>
       <c r="DC28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>160.62951286676105</v>
       </c>
       <c r="DD28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>152.59803722342298</v>
       </c>
       <c r="DE28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>144.96813536225181</v>
       </c>
       <c r="DF28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>137.71972859413921</v>
       </c>
       <c r="DG28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>130.83374216443224</v>
       </c>
       <c r="DH28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>124.29205505621061</v>
       </c>
       <c r="DI28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>118.07745230340008</v>
       </c>
       <c r="DJ28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>112.17357968823006</v>
       </c>
       <c r="DK28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>106.56490070381855</v>
       </c>
       <c r="DL28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>101.23665566862762</v>
       </c>
       <c r="DM28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>96.174822885196235</v>
       </c>
       <c r="DN28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>91.366081740936423</v>
       </c>
       <c r="DO28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>86.797777653889597</v>
       </c>
       <c r="DP28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>82.457888771195115</v>
       </c>
       <c r="DQ28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>78.334994332635361</v>
       </c>
       <c r="DR28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>74.418244616003591</v>
       </c>
       <c r="DS28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>70.69733238520341</v>
       </c>
       <c r="DT28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>67.162465765943239</v>
       </c>
       <c r="DU28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>63.804342477646074</v>
       </c>
       <c r="DV28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>60.614125353763768</v>
       </c>
       <c r="DW28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>57.58341908607558</v>
       </c>
       <c r="DX28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>54.704248131771799</v>
       </c>
       <c r="DY28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>51.969035725183204</v>
       </c>
       <c r="DZ28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>49.370583938924042</v>
       </c>
       <c r="EA28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>46.902054741977835</v>
       </c>
       <c r="EB28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>44.556952004878944</v>
       </c>
       <c r="EC28" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>42.329104404634997</v>
       </c>
     </row>
-    <row r="29" spans="2:133" s="27" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:133" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="48" t="s">
         <v>267</v>
       </c>
@@ -9570,39 +9573,39 @@
         <v>-0.26238024839843976</v>
       </c>
       <c r="D29" s="48">
-        <f t="shared" ref="D29:I29" si="103">D28/D30</f>
+        <f t="shared" ref="D29:I29" si="105">D28/D30</f>
         <v>2.8887451185196155E-2</v>
       </c>
       <c r="E29" s="48">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>-0.25944233932678062</v>
       </c>
       <c r="F29" s="48">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.27127810498258886</v>
       </c>
       <c r="G29" s="48">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>-0.21472944187515691</v>
       </c>
       <c r="H29" s="48">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>-0.41386739009016199</v>
       </c>
       <c r="I29" s="48">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>-0.42038650403928401</v>
       </c>
       <c r="J29" s="48">
-        <f t="shared" ref="J29:L29" si="104">J28/J30</f>
+        <f t="shared" ref="J29:L29" si="106">J28/J30</f>
         <v>-0.43551141754696693</v>
       </c>
       <c r="K29" s="48">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>-0.35478252719874415</v>
       </c>
       <c r="L29" s="48">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>3.1538662527089131E-2</v>
       </c>
       <c r="M29" s="48"/>
@@ -9639,71 +9642,71 @@
       <c r="AR29" s="48"/>
       <c r="AS29" s="48"/>
       <c r="AT29" s="48">
-        <f t="shared" ref="AT29" si="105">+AT28/AT30</f>
+        <f t="shared" ref="AT29" si="107">+AT28/AT30</f>
         <v>0.4276086209702209</v>
       </c>
       <c r="AU29" s="48">
-        <f t="shared" ref="AU29:BC29" si="106">+AU28/AU30</f>
+        <f t="shared" ref="AU29:BC29" si="108">+AU28/AU30</f>
         <v>0.73572906290705742</v>
       </c>
       <c r="AV29" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.75332283464566918</v>
       </c>
       <c r="AW29" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.29261005723336059</v>
       </c>
       <c r="AX29" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.54496844438238001</v>
       </c>
       <c r="AY29" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.65003812514016557</v>
       </c>
       <c r="AZ29" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.49862068040471974</v>
       </c>
       <c r="BA29" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.43539645366343283</v>
       </c>
       <c r="BB29" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.42357676570005259</v>
       </c>
       <c r="BC29" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>0.40169511811302944</v>
       </c>
       <c r="BD29" s="48">
-        <f t="shared" ref="BD29" si="107">+BD28/BD30</f>
+        <f t="shared" ref="BD29" si="109">+BD28/BD30</f>
         <v>1.0198183905091538</v>
       </c>
       <c r="BE29" s="48">
-        <f t="shared" ref="BE29" si="108">+BE28/BE30</f>
+        <f t="shared" ref="BE29" si="110">+BE28/BE30</f>
         <v>1.1194736632665245</v>
       </c>
       <c r="BF29" s="48">
-        <f t="shared" ref="BF29:BJ29" si="109">+BF28/BF30</f>
+        <f t="shared" ref="BF29:BJ29" si="111">+BF28/BF30</f>
         <v>1.1018861249309</v>
       </c>
       <c r="BG29" s="48">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>0.49654298276112585</v>
       </c>
       <c r="BH29" s="48">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>-1.7593949810931593</v>
       </c>
       <c r="BI29" s="48">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>2.7570766349948435</v>
       </c>
       <c r="BJ29" s="48">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>3.0500020409762794</v>
       </c>
       <c r="BK29" s="48"/>
@@ -9717,27 +9720,27 @@
         <v>-1.6693024294998202</v>
       </c>
       <c r="BO29" s="48">
-        <f t="shared" ref="BO29" si="110">BO28/BO30</f>
+        <f t="shared" ref="BO29" si="112">BO28/BO30</f>
         <v>-0.22904265465188936</v>
       </c>
       <c r="BP29" s="48">
-        <f t="shared" ref="BP29" si="111">BP28/BP30</f>
+        <f t="shared" ref="BP29" si="113">BP28/BP30</f>
         <v>-1.4918504921353293</v>
       </c>
       <c r="BQ29" s="48">
-        <f t="shared" ref="BQ29" si="112">BQ28/BQ30</f>
+        <f t="shared" ref="BQ29" si="114">BQ28/BQ30</f>
         <v>1.9905676923077015E-2</v>
       </c>
       <c r="BR29" s="48">
-        <f t="shared" ref="BR29" si="113">BR28/BR30</f>
+        <f t="shared" ref="BR29" si="115">BR28/BR30</f>
         <v>-1.3659311353846153</v>
       </c>
       <c r="BS29" s="48">
-        <f t="shared" ref="BS29:CE29" si="114">BS28/BS30</f>
+        <f t="shared" ref="BS29:CE29" si="116">BS28/BS30</f>
         <v>-0.79832668116923078</v>
       </c>
       <c r="BT29" s="48">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="BU29" s="48"/>
@@ -9747,39 +9750,39 @@
       <c r="BY29" s="48"/>
       <c r="BZ29" s="48"/>
       <c r="CA29" s="48">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>2.2318369497982444</v>
       </c>
       <c r="CB29" s="48">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>9.8397794293600249</v>
       </c>
       <c r="CC29" s="48">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>11.465041918742855</v>
       </c>
       <c r="CD29" s="48">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>13.178071111978081</v>
       </c>
       <c r="CE29" s="48">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>14.966928224337225</v>
       </c>
       <c r="CF29" s="48">
-        <f t="shared" ref="CF29:CH29" si="115">CF28/CF30</f>
+        <f t="shared" ref="CF29:CH29" si="117">CF28/CF30</f>
         <v>16.874413483426668</v>
       </c>
       <c r="CG29" s="48">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>6.7323280760523945</v>
       </c>
       <c r="CH29" s="48">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>2.1396715367185446</v>
       </c>
     </row>
-    <row r="30" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="28" t="s">
         <v>16</v>
       </c>
@@ -9939,23 +9942,23 @@
         <v>220.43599999999998</v>
       </c>
       <c r="CD30" s="9">
-        <f t="shared" ref="CC30:CH30" si="116">+CC30</f>
+        <f t="shared" ref="CD30:CH30" si="118">+CC30</f>
         <v>220.43599999999998</v>
       </c>
       <c r="CE30" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>220.43599999999998</v>
       </c>
       <c r="CF30" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>220.43599999999998</v>
       </c>
       <c r="CG30" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>220.43599999999998</v>
       </c>
       <c r="CH30" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>220.43599999999998</v>
       </c>
       <c r="CK30" s="50" t="s">
@@ -9963,14 +9966,14 @@
       </c>
       <c r="CL30" s="9">
         <f>NPV(CL31,CB28:EC28)+Main!K5-Main!K6</f>
-        <v>16235.154656988063</v>
+        <v>19326.238656988062</v>
       </c>
       <c r="CM30" s="27">
         <f>+CL30/Main!K3</f>
-        <v>84.295539834310262</v>
-      </c>
-    </row>
-    <row r="31" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>95.345108854777607</v>
+      </c>
+    </row>
+    <row r="31" spans="2:133" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
@@ -10041,7 +10044,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="32" spans="2:133" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:133" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B32" s="10" t="s">
         <v>419</v>
       </c>
@@ -10070,31 +10073,31 @@
         <v>0.10288379578170748</v>
       </c>
       <c r="BD32" s="82">
-        <f t="shared" ref="BD32:BJ32" si="117">+BD17/AZ17-1</f>
+        <f t="shared" ref="BD32:BJ32" si="119">+BD17/AZ17-1</f>
         <v>0.22167093039773622</v>
       </c>
       <c r="BE32" s="82">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.11019272369953725</v>
       </c>
       <c r="BF32" s="82">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>0.12784766365562605</v>
       </c>
       <c r="BG32" s="82">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>5.7809522514044698E-2</v>
       </c>
       <c r="BH32" s="82">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>9.3387875676977927E-2</v>
       </c>
       <c r="BI32" s="82">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>7.0836486966986634E-2</v>
       </c>
       <c r="BJ32" s="82">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>7.3890181452151094E-2</v>
       </c>
       <c r="CB32" s="82">
@@ -10102,27 +10105,27 @@
         <v>0.14343136545402246</v>
       </c>
       <c r="CC32" s="82">
-        <f t="shared" ref="CC32:CH32" si="118">+CC17/CB17-1</f>
+        <f t="shared" ref="CC32:CH32" si="120">+CC17/CB17-1</f>
         <v>7.2166999069091409E-2</v>
       </c>
       <c r="CD32" s="82">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>9.3121684615286915E-2</v>
       </c>
       <c r="CE32" s="82">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>9.6159593538961197E-2</v>
       </c>
       <c r="CF32" s="82">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>9.9270488958910219E-2</v>
       </c>
       <c r="CG32" s="82">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>-0.57591984016050723</v>
       </c>
       <c r="CH32" s="82">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>-0.62521851428844677</v>
       </c>
       <c r="CK32" s="10" t="s">
@@ -10132,7 +10135,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="33" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="50" t="s">
         <v>602</v>
       </c>
@@ -10184,19 +10187,19 @@
       <c r="AV33" s="28"/>
       <c r="AW33" s="45"/>
       <c r="AX33" s="45">
-        <f t="shared" ref="AX33:BA33" si="119">+AX9/AT9-1</f>
+        <f t="shared" ref="AX33:BA33" si="121">+AX9/AT9-1</f>
         <v>0.14604493869006863</v>
       </c>
       <c r="AY33" s="45">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.16910523716475945</v>
       </c>
       <c r="AZ33" s="45">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.12969918061449204</v>
       </c>
       <c r="BA33" s="45">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>0.13194293470814222</v>
       </c>
       <c r="BB33" s="45">
@@ -10208,31 +10211,31 @@
         <v>6.5210923036233881E-2</v>
       </c>
       <c r="BD33" s="45">
-        <f t="shared" ref="BD33:BJ33" si="120">+BD9/AZ9-1</f>
+        <f t="shared" ref="BD33:BJ33" si="122">+BD9/AZ9-1</f>
         <v>0.14173469438974151</v>
       </c>
       <c r="BE33" s="45">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>2.6883690152438078E-2</v>
       </c>
       <c r="BF33" s="45">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>7.3566818482979635E-2</v>
       </c>
       <c r="BG33" s="45">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>-1.4017990616739806E-2</v>
       </c>
       <c r="BH33" s="45">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>3.4568512743557767E-2</v>
       </c>
       <c r="BI33" s="45">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BJ33" s="45">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK33" s="28"/>
@@ -10242,27 +10245,27 @@
         <v>0.10000000000000009</v>
       </c>
       <c r="CC33" s="26">
-        <f t="shared" ref="CC33:CH33" si="121">+CC9/CB9-1</f>
+        <f t="shared" ref="CC33:CH33" si="123">+CC9/CB9-1</f>
         <v>-1.0430630747911396E-2</v>
       </c>
       <c r="CD33" s="26">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="CE33" s="26">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="CF33" s="26">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="CG33" s="26">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.8</v>
       </c>
       <c r="CH33" s="26">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>-0.8</v>
       </c>
       <c r="CK33" s="50" t="s">
@@ -10272,7 +10275,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="34" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="50" t="s">
         <v>420</v>
       </c>
@@ -10320,71 +10323,71 @@
       <c r="AR34" s="28"/>
       <c r="AS34" s="28"/>
       <c r="AT34" s="45">
-        <f t="shared" ref="AT34" si="122">AT19/AT17</f>
+        <f t="shared" ref="AT34" si="124">AT19/AT17</f>
         <v>0.95483062034498445</v>
       </c>
       <c r="AU34" s="45">
-        <f t="shared" ref="AU34:BC34" si="123">AU19/AU17</f>
+        <f t="shared" ref="AU34:BC34" si="125">AU19/AU17</f>
         <v>0.96098015934700143</v>
       </c>
       <c r="AV34" s="45">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.95356986799135268</v>
       </c>
       <c r="AW34" s="45">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.95634245816446795</v>
       </c>
       <c r="AX34" s="45">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.95339132659902837</v>
       </c>
       <c r="AY34" s="45">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.95005830327248419</v>
       </c>
       <c r="AZ34" s="45">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.94295473363731874</v>
       </c>
       <c r="BA34" s="45">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.9410654400627716</v>
       </c>
       <c r="BB34" s="45">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.94086985613917695</v>
       </c>
       <c r="BC34" s="45">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.9373430298773423</v>
       </c>
       <c r="BD34" s="45">
-        <f t="shared" ref="BD34:BJ34" si="124">BD19/BD17</f>
+        <f t="shared" ref="BD34:BJ34" si="126">BD19/BD17</f>
         <v>0.93489487853678466</v>
       </c>
       <c r="BE34" s="45">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>0.94101474248516181</v>
       </c>
       <c r="BF34" s="45">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>0.93713791886218389</v>
       </c>
       <c r="BG34" s="45">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>0.9357521784569488</v>
       </c>
       <c r="BH34" s="45">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>0.93207340008565198</v>
       </c>
       <c r="BI34" s="45">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>0.93</v>
       </c>
       <c r="BJ34" s="45">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>0.93</v>
       </c>
       <c r="BK34" s="28"/>
@@ -10394,35 +10397,35 @@
         <v>0.95000000000000007</v>
       </c>
       <c r="CB34" s="26">
-        <f t="shared" ref="CB34:CH34" si="125">+CB19/CB17</f>
+        <f t="shared" ref="CB34:CH34" si="127">+CB19/CB17</f>
         <v>0.95000000000000007</v>
       </c>
       <c r="CC34" s="26">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>0.95000000000000007</v>
       </c>
       <c r="CD34" s="26">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>0.95</v>
       </c>
       <c r="CE34" s="26">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>0.95</v>
       </c>
       <c r="CF34" s="26">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>0.95</v>
       </c>
       <c r="CG34" s="26">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>0.95</v>
       </c>
       <c r="CH34" s="26">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>0.95</v>
       </c>
     </row>
-    <row r="35" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
@@ -10487,7 +10490,7 @@
       <c r="BK35" s="28"/>
       <c r="BL35" s="28"/>
     </row>
-    <row r="36" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="50" t="s">
         <v>367</v>
       </c>
@@ -10569,7 +10572,7 @@
         <v>972400</v>
       </c>
     </row>
-    <row r="37" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
       <c r="E37" s="28"/>
@@ -10633,7 +10636,7 @@
       <c r="BK37" s="28"/>
       <c r="BL37" s="28"/>
     </row>
-    <row r="38" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="50" t="s">
         <v>366</v>
       </c>
@@ -10704,39 +10707,39 @@
         <v>-178384</v>
       </c>
       <c r="BN38" s="9">
-        <f t="shared" ref="BN38:BP38" si="126">BN39+BN40-BN59</f>
+        <f t="shared" ref="BN38:BP38" si="128">BN39+BN40-BN59</f>
         <v>87016</v>
       </c>
       <c r="BO38" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>168612</v>
       </c>
       <c r="BP38" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>-19265</v>
       </c>
       <c r="BQ38" s="9">
-        <f t="shared" ref="BQ38:BU38" si="127">BP38+BQ28</f>
+        <f t="shared" ref="BQ38:BU38" si="129">BP38+BQ28</f>
         <v>-16677.261999999988</v>
       </c>
       <c r="BR38" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>-194248.30959999998</v>
       </c>
       <c r="BS38" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>-298030.77815199998</v>
       </c>
       <c r="BT38" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>-298030.77815199998</v>
       </c>
       <c r="BU38" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="129"/>
         <v>-298030.77815199998</v>
       </c>
     </row>
-    <row r="39" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="50" t="s">
         <v>17</v>
       </c>
@@ -10852,7 +10855,7 @@
         <v>277594</v>
       </c>
     </row>
-    <row r="40" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="50" t="s">
         <v>17</v>
       </c>
@@ -10961,7 +10964,7 @@
         <v>19294</v>
       </c>
     </row>
-    <row r="41" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:90" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="28" t="s">
         <v>252</v>
       </c>
@@ -11063,7 +11066,7 @@
         <v>6415</v>
       </c>
     </row>
-    <row r="42" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="28" t="s">
         <v>253</v>
       </c>
@@ -11113,7 +11116,7 @@
         <v>7475</v>
       </c>
     </row>
-    <row r="43" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="28" t="s">
         <v>254</v>
       </c>
@@ -11164,7 +11167,7 @@
       </c>
       <c r="BZ43" s="45"/>
     </row>
-    <row r="44" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="50" t="s">
         <v>363</v>
       </c>
@@ -11186,7 +11189,7 @@
         <v>3536</v>
       </c>
     </row>
-    <row r="45" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="50" t="s">
         <v>423</v>
       </c>
@@ -11194,7 +11197,7 @@
         <v>27.391999999999999</v>
       </c>
     </row>
-    <row r="46" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="50" t="s">
         <v>422</v>
       </c>
@@ -11203,7 +11206,7 @@
         <v>300.964</v>
       </c>
     </row>
-    <row r="47" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="50" t="s">
         <v>265</v>
       </c>
@@ -11211,7 +11214,7 @@
         <v>465.36900000000003</v>
       </c>
     </row>
-    <row r="48" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:90" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="28" t="s">
         <v>163</v>
       </c>
@@ -11318,7 +11321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:81" s="50" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:81" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="50" t="s">
         <v>421</v>
       </c>
@@ -11327,39 +11330,39 @@
         <v>502663</v>
       </c>
       <c r="D49" s="50">
-        <f t="shared" ref="D49:L49" si="128">SUM(D39:D48)</f>
+        <f t="shared" ref="D49:L49" si="130">SUM(D39:D48)</f>
         <v>493680</v>
       </c>
       <c r="E49" s="50">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>464640</v>
       </c>
       <c r="F49" s="50">
-        <f t="shared" ref="F49" si="129">SUM(F39:F48)</f>
+        <f t="shared" ref="F49" si="131">SUM(F39:F48)</f>
         <v>489581</v>
       </c>
       <c r="G49" s="50">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>459606</v>
       </c>
       <c r="H49" s="50">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>416663</v>
       </c>
       <c r="I49" s="50">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>371224</v>
       </c>
       <c r="J49" s="50">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>328962</v>
       </c>
       <c r="K49" s="50">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>293593</v>
       </c>
       <c r="L49" s="50">
-        <f t="shared" si="128"/>
+        <f t="shared" si="130"/>
         <v>311971</v>
       </c>
       <c r="AY49" s="50">
@@ -11371,23 +11374,23 @@
         <v>232388</v>
       </c>
       <c r="BN49" s="50">
-        <f t="shared" ref="BN49:BP49" si="130">SUM(BN39:BN48)</f>
+        <f t="shared" ref="BN49:BP49" si="132">SUM(BN39:BN48)</f>
         <v>712390</v>
       </c>
       <c r="BO49" s="50">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>489581</v>
       </c>
       <c r="BP49" s="50">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>328962</v>
       </c>
     </row>
-    <row r="50" spans="2:81" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:81" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="BY50" s="28"/>
       <c r="BZ50" s="28"/>
     </row>
-    <row r="51" spans="2:81" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:81" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="50" t="s">
         <v>424</v>
       </c>
@@ -11487,7 +11490,7 @@
         <v>14939</v>
       </c>
     </row>
-    <row r="52" spans="2:81" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:81" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="50" t="s">
         <v>425</v>
       </c>
@@ -11587,7 +11590,7 @@
         <v>21856</v>
       </c>
     </row>
-    <row r="53" spans="2:81" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:81" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="28" t="s">
         <v>167</v>
       </c>
@@ -11689,7 +11692,7 @@
       <c r="BY53" s="9"/>
       <c r="BZ53" s="9"/>
     </row>
-    <row r="54" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="50" t="s">
         <v>426</v>
       </c>
@@ -11792,7 +11795,7 @@
       <c r="BY54" s="28"/>
       <c r="BZ54" s="28"/>
     </row>
-    <row r="55" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="50" t="s">
         <v>427</v>
       </c>
@@ -11862,7 +11865,7 @@
       <c r="BY55" s="28"/>
       <c r="BZ55" s="28"/>
     </row>
-    <row r="56" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="28" t="s">
         <v>255</v>
       </c>
@@ -11938,7 +11941,7 @@
       <c r="BZ56" s="28"/>
       <c r="CA56" s="28"/>
     </row>
-    <row r="57" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="50" t="s">
         <v>428</v>
       </c>
@@ -11961,7 +11964,7 @@
       <c r="BZ57" s="28"/>
       <c r="CA57" s="28"/>
     </row>
-    <row r="58" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="28" t="s">
         <v>170</v>
       </c>
@@ -12006,7 +12009,7 @@
       <c r="BZ58" s="28"/>
       <c r="CA58" s="28"/>
     </row>
-    <row r="59" spans="2:81" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:81" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="28" t="s">
         <v>256</v>
       </c>
@@ -12070,7 +12073,7 @@
         <v>316153</v>
       </c>
     </row>
-    <row r="60" spans="2:81" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:81" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="28" t="s">
         <v>174</v>
       </c>
@@ -12087,7 +12090,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="61" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="28" t="s">
         <v>175</v>
       </c>
@@ -12100,35 +12103,35 @@
         <v>598464</v>
       </c>
       <c r="E61" s="9">
-        <f t="shared" ref="E61:L61" si="131">SUM(E51:E59)</f>
+        <f t="shared" ref="E61:L61" si="133">SUM(E51:E59)</f>
         <v>593548</v>
       </c>
       <c r="F61" s="28">
-        <f t="shared" ref="F61" si="132">SUM(F51:F60)</f>
+        <f t="shared" ref="F61" si="134">SUM(F51:F60)</f>
         <v>578225</v>
       </c>
       <c r="G61" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>563584</v>
       </c>
       <c r="H61" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>552947</v>
       </c>
       <c r="I61" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>552244</v>
       </c>
       <c r="J61" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>556038</v>
       </c>
       <c r="K61" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>542450</v>
       </c>
       <c r="L61" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>529159</v>
       </c>
       <c r="AY61" s="9">
@@ -12141,15 +12144,15 @@
         <v>453138</v>
       </c>
       <c r="BN61" s="28">
-        <f t="shared" ref="BN61:BO61" si="133">SUM(BN51:BN60)</f>
+        <f t="shared" ref="BN61:BO61" si="135">SUM(BN51:BN60)</f>
         <v>814774</v>
       </c>
       <c r="BO61" s="28">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>578225</v>
       </c>
       <c r="BP61" s="9">
-        <f t="shared" ref="BP61" si="134">SUM(BP51:BP59)</f>
+        <f t="shared" ref="BP61" si="136">SUM(BP51:BP59)</f>
         <v>556038</v>
       </c>
       <c r="BQ61" s="28"/>
@@ -12164,7 +12167,7 @@
       <c r="BZ61" s="28"/>
       <c r="CA61" s="28"/>
     </row>
-    <row r="62" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="28" t="s">
         <v>257</v>
       </c>
@@ -12223,7 +12226,7 @@
       <c r="BX62" s="28"/>
       <c r="CA62" s="28"/>
     </row>
-    <row r="63" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="28" t="s">
         <v>258</v>
       </c>
@@ -12273,7 +12276,7 @@
         <v>1380725</v>
       </c>
     </row>
-    <row r="64" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:81" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="28" t="s">
         <v>259</v>
       </c>
@@ -12332,7 +12335,7 @@
       </c>
       <c r="CC64" s="28"/>
     </row>
-    <row r="65" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="28" t="s">
         <v>260</v>
       </c>
@@ -12382,35 +12385,35 @@
         <v>-1609570</v>
       </c>
       <c r="BQ65" s="9">
-        <f t="shared" ref="BQ65:BX65" si="135">BP65+BQ28</f>
+        <f t="shared" ref="BQ65:BX65" si="137">BP65+BQ28</f>
         <v>-1606982.2620000001</v>
       </c>
       <c r="BR65" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>-1784553.3096</v>
       </c>
       <c r="BS65" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>-1888335.7781520002</v>
       </c>
       <c r="BT65" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>-1888335.7781520002</v>
       </c>
       <c r="BU65" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>-1888335.7781520002</v>
       </c>
       <c r="BV65" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>-1888335.7781520002</v>
       </c>
       <c r="BW65" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>-1888335.7781520002</v>
       </c>
       <c r="BX65" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>-1888335.7781520002</v>
       </c>
       <c r="CA65" s="9">
@@ -12434,7 +12437,7 @@
         <v>-1876901.3857250998</v>
       </c>
     </row>
-    <row r="66" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="28" t="s">
         <v>176</v>
       </c>
@@ -12443,39 +12446,39 @@
         <v>-114413</v>
       </c>
       <c r="D66" s="9">
-        <f t="shared" ref="D66:I66" si="136">SUM(D62:D65)</f>
+        <f t="shared" ref="D66:I66" si="138">SUM(D62:D65)</f>
         <v>-104783</v>
       </c>
       <c r="E66" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>-128908</v>
       </c>
       <c r="F66" s="9">
-        <f t="shared" ref="F66" si="137">SUM(F62:F65)</f>
+        <f t="shared" ref="F66" si="139">SUM(F62:F65)</f>
         <v>-88644</v>
       </c>
       <c r="G66" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>-103978</v>
       </c>
       <c r="H66" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>-136284</v>
       </c>
       <c r="I66" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>-181020</v>
       </c>
       <c r="J66" s="9">
-        <f t="shared" ref="J66:L66" si="138">SUM(J62:J65)</f>
+        <f t="shared" ref="J66:L66" si="140">SUM(J62:J65)</f>
         <v>-227077</v>
       </c>
       <c r="K66" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>-248857</v>
       </c>
       <c r="L66" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>-217188</v>
       </c>
       <c r="AY66" s="9">
@@ -12487,20 +12490,20 @@
         <v>-220750</v>
       </c>
       <c r="BN66" s="9">
-        <f t="shared" ref="BN66:BP66" si="139">SUM(BN62:BN65)</f>
+        <f t="shared" ref="BN66:BP66" si="141">SUM(BN62:BN65)</f>
         <v>-102384</v>
       </c>
       <c r="BO66" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>-88644</v>
       </c>
       <c r="BP66" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>-227077</v>
       </c>
       <c r="CC66" s="28"/>
     </row>
-    <row r="67" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="50" t="s">
         <v>429</v>
       </c>
@@ -12509,39 +12512,39 @@
         <v>502663</v>
       </c>
       <c r="D67" s="9">
-        <f t="shared" ref="D67:I67" si="140">D66+D61</f>
+        <f t="shared" ref="D67:I67" si="142">D66+D61</f>
         <v>493681</v>
       </c>
       <c r="E67" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>464640</v>
       </c>
       <c r="F67" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>489581</v>
       </c>
       <c r="G67" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>459606</v>
       </c>
       <c r="H67" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>416663</v>
       </c>
       <c r="I67" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>371224</v>
       </c>
       <c r="J67" s="9">
-        <f t="shared" ref="J67:L67" si="141">J66+J61</f>
+        <f t="shared" ref="J67:L67" si="143">J66+J61</f>
         <v>328961</v>
       </c>
       <c r="K67" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>293593</v>
       </c>
       <c r="L67" s="9">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>311971</v>
       </c>
       <c r="AY67" s="9">
@@ -12553,21 +12556,21 @@
         <v>232388</v>
       </c>
       <c r="BN67" s="9">
-        <f t="shared" ref="BN67:BP67" si="142">BN66+BN61</f>
+        <f t="shared" ref="BN67:BP67" si="144">BN66+BN61</f>
         <v>712390</v>
       </c>
       <c r="BO67" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>489581</v>
       </c>
       <c r="BP67" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>328961</v>
       </c>
       <c r="CC67" s="28"/>
     </row>
-    <row r="68" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="50" t="s">
         <v>430</v>
       </c>
@@ -12576,7 +12579,7 @@
         <v>144.9259999999999</v>
       </c>
     </row>
-    <row r="70" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="50" t="s">
         <v>436</v>
       </c>
@@ -12584,7 +12587,7 @@
         <v>37.991999999999997</v>
       </c>
     </row>
-    <row r="71" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="50" t="s">
         <v>220</v>
       </c>
@@ -12592,7 +12595,7 @@
         <v>16.437999999999999</v>
       </c>
     </row>
-    <row r="72" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="50" t="s">
         <v>432</v>
       </c>
@@ -12600,7 +12603,7 @@
         <v>43.841000000000001</v>
       </c>
     </row>
-    <row r="73" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="50" t="s">
         <v>433</v>
       </c>
@@ -12608,7 +12611,7 @@
         <v>2.1059999999999999</v>
       </c>
     </row>
-    <row r="74" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="50" t="s">
         <v>163</v>
       </c>
@@ -12616,7 +12619,7 @@
         <v>2.0910000000000002</v>
       </c>
     </row>
-    <row r="75" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="50" t="s">
         <v>434</v>
       </c>
@@ -12624,7 +12627,7 @@
         <v>46.585000000000001</v>
       </c>
     </row>
-    <row r="76" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B76" s="50" t="s">
         <v>435</v>
       </c>
@@ -12632,7 +12635,7 @@
         <v>6.3819999999999997</v>
       </c>
     </row>
-    <row r="77" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="50" t="s">
         <v>437</v>
       </c>
@@ -12641,7 +12644,7 @@
         <v>60.305999999999997</v>
       </c>
     </row>
-    <row r="78" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="50" t="s">
         <v>431</v>
       </c>
@@ -12650,8 +12653,8 @@
         <v>215.74099999999999</v>
       </c>
     </row>
-    <row r="79" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="2:83" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="50" t="s">
         <v>438</v>
       </c>
@@ -12659,7 +12662,7 @@
         <v>-17.006</v>
       </c>
     </row>
-    <row r="81" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="50" t="s">
         <v>439</v>
       </c>
@@ -12667,7 +12670,7 @@
         <v>0.25800000000000001</v>
       </c>
     </row>
-    <row r="82" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="50" t="s">
         <v>440</v>
       </c>
@@ -12676,8 +12679,8 @@
         <v>-16.748000000000001</v>
       </c>
     </row>
-    <row r="83" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="84" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="50" t="s">
         <v>443</v>
       </c>
@@ -12685,7 +12688,7 @@
         <v>16.398</v>
       </c>
     </row>
-    <row r="85" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="50" t="s">
         <v>444</v>
       </c>
@@ -12693,7 +12696,7 @@
         <v>-2.161</v>
       </c>
     </row>
-    <row r="86" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B86" s="50" t="s">
         <v>423</v>
       </c>
@@ -12701,7 +12704,7 @@
         <v>-0.66800000000000004</v>
       </c>
     </row>
-    <row r="87" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="50" t="s">
         <v>435</v>
       </c>
@@ -12709,7 +12712,7 @@
         <v>-13.473000000000001</v>
       </c>
     </row>
-    <row r="88" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B88" s="50" t="s">
         <v>445</v>
       </c>
@@ -12718,7 +12721,7 @@
         <v>9.6000000000000085E-2</v>
       </c>
     </row>
-    <row r="89" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="50" t="s">
         <v>442</v>
       </c>
@@ -12726,7 +12729,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="90" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="50" t="s">
         <v>441</v>
       </c>
@@ -12735,31 +12738,31 @@
         <v>199.29899999999998</v>
       </c>
     </row>
-    <row r="91" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="28"/>
     </row>
-    <row r="92" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="28"/>
     </row>
-    <row r="93" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="28"/>
     </row>
-    <row r="94" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="28"/>
     </row>
-    <row r="95" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="28"/>
     </row>
-    <row r="96" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:51" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="28"/>
     </row>
-    <row r="97" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="28"/>
     </row>
-    <row r="98" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="28"/>
     </row>
-    <row r="99" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:78" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
       <c r="D99" s="10"/>
@@ -12825,16 +12828,16 @@
       <c r="BN99" s="10"/>
       <c r="BO99" s="10"/>
     </row>
-    <row r="100" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B100" s="28"/>
     </row>
-    <row r="101" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B101" s="28"/>
     </row>
-    <row r="102" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B102" s="28"/>
     </row>
-    <row r="103" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:78" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
       <c r="D103" s="10"/>
@@ -12900,19 +12903,19 @@
       <c r="BN103" s="10"/>
       <c r="BO103" s="10"/>
     </row>
-    <row r="104" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="28"/>
     </row>
-    <row r="105" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B105" s="28"/>
     </row>
-    <row r="106" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B106" s="28"/>
     </row>
-    <row r="107" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B107" s="28"/>
     </row>
-    <row r="108" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:78" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
       <c r="D108" s="10"/>
@@ -12978,12 +12981,12 @@
       <c r="BN108" s="10"/>
       <c r="BO108" s="10"/>
     </row>
-    <row r="109" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:78" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B109" s="28"/>
       <c r="BY109"/>
       <c r="BZ109"/>
     </row>
-    <row r="110" spans="2:78" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:78" x14ac:dyDescent="0.25">
       <c r="B110" s="31"/>
       <c r="C110" s="33"/>
       <c r="D110" s="33"/>
@@ -13049,7 +13052,7 @@
       <c r="BN110" s="33"/>
       <c r="BO110" s="33"/>
     </row>
-    <row r="111" spans="2:78" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:78" x14ac:dyDescent="0.25">
       <c r="B111" s="31"/>
       <c r="C111" s="33"/>
       <c r="D111" s="33"/>
@@ -13129,19 +13132,19 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="12.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
@@ -13149,7 +13152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
@@ -13157,32 +13160,32 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
@@ -13190,17 +13193,17 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
@@ -13218,19 +13221,19 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="12.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
@@ -13238,12 +13241,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -13251,7 +13254,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -13259,17 +13262,17 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
@@ -13277,42 +13280,42 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C12" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
         <v>40</v>
       </c>
@@ -13330,19 +13333,19 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="12.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
@@ -13350,12 +13353,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -13363,7 +13366,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -13371,7 +13374,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
@@ -13379,17 +13382,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
@@ -13397,17 +13400,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C11" s="16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
@@ -13425,24 +13428,24 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:CO83"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" customWidth="1"/>
-    <col min="4" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" customWidth="1"/>
+    <col min="4" max="10" width="10.7265625" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C2" s="40" t="s">
         <v>153</v>
       </c>
@@ -13525,7 +13528,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B3" s="31" t="s">
         <v>150</v>
       </c>
@@ -13610,7 +13613,7 @@
         <v>37374.314509560041</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B4" s="31" t="s">
         <v>65</v>
       </c>
@@ -13696,7 +13699,7 @@
         <v>26162.020156692026</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B5" s="31" t="s">
         <v>242</v>
       </c>
@@ -13761,7 +13764,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
         <v>246</v>
       </c>
@@ -13840,7 +13843,7 @@
         <v>1868.7157254780022</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
         <v>66</v>
       </c>
@@ -13914,7 +13917,7 @@
         <v>134.00956406250003</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
         <v>243</v>
       </c>
@@ -13995,7 +13998,7 @@
         <v>250.42577972804557</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
         <v>241</v>
       </c>
@@ -14075,7 +14078,7 @@
         <v>33571.106326655616</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
         <v>65</v>
       </c>
@@ -14161,7 +14164,7 @@
         <v>18687.157254780021</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
         <v>242</v>
       </c>
@@ -14228,7 +14231,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B12" s="31" t="s">
         <v>246</v>
       </c>
@@ -14314,7 +14317,7 @@
         <v>1678.5553163327809</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
         <v>66</v>
       </c>
@@ -14396,7 +14399,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
         <v>243</v>
       </c>
@@ -14482,7 +14485,7 @@
         <v>167.8555316332781</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
         <v>244</v>
       </c>
@@ -14553,7 +14556,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B16" s="31" t="s">
         <v>245</v>
       </c>
@@ -14639,7 +14642,7 @@
         <v>33.571106326655624</v>
       </c>
     </row>
-    <row r="17" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:93" x14ac:dyDescent="0.25">
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
@@ -14663,7 +14666,7 @@
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
     </row>
-    <row r="18" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:93" x14ac:dyDescent="0.25">
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
@@ -14687,7 +14690,7 @@
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
     </row>
-    <row r="19" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
       <c r="D19" s="31"/>
@@ -14712,7 +14715,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
     </row>
-    <row r="20" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B20" s="31" t="s">
         <v>180</v>
       </c>
@@ -14803,7 +14806,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B21" s="31" t="s">
         <v>179</v>
       </c>
@@ -14894,7 +14897,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="2:93" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:93" s="8" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>67</v>
       </c>
@@ -14988,7 +14991,7 @@
         <v>283996.88605470117</v>
       </c>
     </row>
-    <row r="23" spans="2:93" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:93" s="8" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>178</v>
       </c>
@@ -15085,7 +15088,7 @@
         <v>289196.88605470117</v>
       </c>
     </row>
-    <row r="24" spans="2:93" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:93" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="31" t="s">
         <v>181</v>
       </c>
@@ -15178,7 +15181,7 @@
         <v>14199.844302735059</v>
       </c>
     </row>
-    <row r="25" spans="2:93" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:93" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="31" t="s">
         <v>182</v>
       </c>
@@ -15265,7 +15268,7 @@
         <v>68891.606101919999</v>
       </c>
     </row>
-    <row r="26" spans="2:93" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:93" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="31" t="s">
         <v>183</v>
       </c>
@@ -15356,7 +15359,7 @@
         <v>20032.658926505152</v>
       </c>
     </row>
-    <row r="27" spans="2:93" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:93" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="31" t="s">
         <v>184</v>
       </c>
@@ -15453,7 +15456,7 @@
         <v>34232.50322924021</v>
       </c>
     </row>
-    <row r="28" spans="2:93" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:93" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="31" t="s">
         <v>146</v>
       </c>
@@ -15550,7 +15553,7 @@
         <v>254964.38282546095</v>
       </c>
     </row>
-    <row r="29" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B29" s="31" t="s">
         <v>185</v>
       </c>
@@ -15619,7 +15622,7 @@
       <c r="W29" s="9"/>
       <c r="X29" s="9"/>
     </row>
-    <row r="30" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B30" s="31" t="s">
         <v>147</v>
       </c>
@@ -15717,7 +15720,7 @@
         <v>254964.38282546095</v>
       </c>
     </row>
-    <row r="31" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B31" s="31" t="s">
         <v>188</v>
       </c>
@@ -15808,7 +15811,7 @@
         <v>89237.533988911324</v>
       </c>
     </row>
-    <row r="32" spans="2:93" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:93" s="8" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>20</v>
       </c>
@@ -16173,7 +16176,7 @@
         <v>5331.8070801802987</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33" s="31" t="s">
         <v>187</v>
       </c>
@@ -16271,7 +16274,7 @@
         <v>1.2747587841899914</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B34" s="31" t="s">
         <v>186</v>
       </c>
@@ -16361,10 +16364,10 @@
         <v>130006.43799591932</v>
       </c>
     </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B35" s="31"/>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>156</v>
       </c>
@@ -16401,7 +16404,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>157</v>
       </c>
@@ -16436,7 +16439,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>158</v>
       </c>
@@ -16472,7 +16475,7 @@
         <v>2655264.7103621415</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>159</v>
       </c>
@@ -16508,7 +16511,7 @@
         <v>21.764464839033948</v>
       </c>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>160</v>
       </c>
@@ -16537,7 +16540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>161</v>
       </c>
@@ -16571,7 +16574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>157</v>
       </c>
@@ -16600,7 +16603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>158</v>
       </c>
@@ -16629,7 +16632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>162</v>
       </c>
@@ -16658,7 +16661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>163</v>
       </c>
@@ -16687,7 +16690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>164</v>
       </c>
@@ -16723,7 +16726,7 @@
         <v>489581</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
       <c r="E47" s="32"/>
       <c r="F47" s="33"/>
       <c r="G47" s="33"/>
@@ -16731,7 +16734,7 @@
       <c r="I47" s="33"/>
       <c r="J47" s="33"/>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>165</v>
       </c>
@@ -16760,7 +16763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>166</v>
       </c>
@@ -16789,7 +16792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>167</v>
       </c>
@@ -16818,7 +16821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>168</v>
       </c>
@@ -16847,7 +16850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>169</v>
       </c>
@@ -16876,7 +16879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>170</v>
       </c>
@@ -16905,7 +16908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>171</v>
       </c>
@@ -16939,7 +16942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>172</v>
       </c>
@@ -16970,7 +16973,7 @@
         <v>276445</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>173</v>
       </c>
@@ -17001,7 +17004,7 @@
         <v>16987</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>169</v>
       </c>
@@ -17030,7 +17033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>174</v>
       </c>
@@ -17059,7 +17062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>175</v>
       </c>
@@ -17093,7 +17096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>176</v>
       </c>
@@ -17124,7 +17127,7 @@
         <v>-88644</v>
       </c>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>177</v>
       </c>
@@ -17161,7 +17164,7 @@
         <v>489581</v>
       </c>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B63" s="31" t="s">
         <v>218</v>
       </c>
@@ -17194,7 +17197,7 @@
         <v>-31844</v>
       </c>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B64" s="31" t="s">
         <v>219</v>
       </c>
@@ -17225,7 +17228,7 @@
         <v>-519</v>
       </c>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B65" s="31" t="s">
         <v>220</v>
       </c>
@@ -17255,7 +17258,7 @@
         <v>23159</v>
       </c>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B66" s="31" t="s">
         <v>221</v>
       </c>
@@ -17285,7 +17288,7 @@
         <v>15235</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B67" s="31" t="s">
         <v>222</v>
       </c>
@@ -17315,7 +17318,7 @@
         <v>15235</v>
       </c>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B68" s="31" t="s">
         <v>236</v>
       </c>
@@ -17346,7 +17349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B69" s="31" t="s">
         <v>223</v>
       </c>
@@ -17377,7 +17380,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B70" s="31" t="s">
         <v>224</v>
       </c>
@@ -17409,7 +17412,7 @@
         <v>102805</v>
       </c>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:14" ht="13" x14ac:dyDescent="0.3">
       <c r="B71" s="8" t="s">
         <v>225</v>
       </c>
@@ -17442,7 +17445,7 @@
         <v>124205</v>
       </c>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B72" s="31" t="s">
         <v>226</v>
       </c>
@@ -17472,7 +17475,7 @@
         <v>-1870</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B73" s="31" t="s">
         <v>157</v>
       </c>
@@ -17503,7 +17506,7 @@
         <v>18415</v>
       </c>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B74" s="31" t="s">
         <v>163</v>
       </c>
@@ -17533,7 +17536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:14" ht="13" x14ac:dyDescent="0.3">
       <c r="B75" s="8" t="s">
         <v>227</v>
       </c>
@@ -17566,7 +17569,7 @@
         <v>16545</v>
       </c>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B76" s="31" t="s">
         <v>228</v>
       </c>
@@ -17596,7 +17599,7 @@
         <v>14044</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B77" s="31" t="s">
         <v>229</v>
       </c>
@@ -17626,7 +17629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="31" t="s">
         <v>230</v>
       </c>
@@ -17656,7 +17659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B79" s="31" t="s">
         <v>231</v>
       </c>
@@ -17687,7 +17690,7 @@
         <v>-158644</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" ht="13" x14ac:dyDescent="0.3">
       <c r="B80" s="8" t="s">
         <v>232</v>
       </c>
@@ -17720,7 +17723,7 @@
         <v>14044</v>
       </c>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B81" s="31" t="s">
         <v>233</v>
       </c>
@@ -17753,7 +17756,7 @@
         <v>154794</v>
       </c>
     </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B82" s="31" t="s">
         <v>234</v>
       </c>
@@ -17785,7 +17788,7 @@
         <v>449824</v>
       </c>
     </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B83" s="31" t="s">
         <v>235</v>
       </c>
@@ -17833,29 +17836,29 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -17880,7 +17883,7 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>79</v>
       </c>
@@ -17905,7 +17908,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>79</v>
       </c>
@@ -17930,7 +17933,7 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>79</v>
       </c>
@@ -17955,7 +17958,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>79</v>
       </c>
@@ -17980,7 +17983,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>79</v>
       </c>
@@ -18005,7 +18008,7 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>57</v>
       </c>
@@ -18030,7 +18033,7 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>57</v>
       </c>
@@ -18055,7 +18058,7 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>90</v>
       </c>
@@ -18078,7 +18081,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>111</v>
       </c>
@@ -18103,7 +18106,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>89</v>
       </c>
@@ -18126,7 +18129,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>89</v>
       </c>
@@ -18149,7 +18152,7 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>107</v>
       </c>
@@ -18174,7 +18177,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>91</v>
       </c>
@@ -18191,7 +18194,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>92</v>
       </c>
@@ -18206,7 +18209,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>103</v>
       </c>
@@ -18223,7 +18226,7 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>114</v>
       </c>
@@ -18235,14 +18238,14 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -18263,20 +18266,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O102"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="12"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="9.1796875" style="12"/>
+    <col min="4" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
@@ -18284,7 +18287,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
@@ -18292,7 +18295,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -18300,32 +18303,32 @@
         <v>317</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C5" s="12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C6" s="12" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C8" s="12" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" s="12" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>144</v>
       </c>
@@ -18333,12 +18336,12 @@
         <v>318</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" s="12" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
@@ -18346,12 +18349,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C13" s="12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
@@ -18359,7 +18362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
@@ -18367,12 +18370,12 @@
         <v>607</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C16" s="12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>14</v>
       </c>
@@ -18380,7 +18383,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
@@ -18388,17 +18391,17 @@
         <v>605</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C19" s="54" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="12" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C21" s="49"/>
       <c r="D21" s="49" t="s">
         <v>294</v>
@@ -18407,7 +18410,7 @@
       <c r="F21" s="49"/>
       <c r="G21" s="49"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C22" s="49"/>
       <c r="D22" s="49" t="s">
         <v>295</v>
@@ -18425,7 +18428,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C23" s="49" t="s">
         <v>298</v>
       </c>
@@ -18445,7 +18448,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C24" s="49" t="s">
         <v>303</v>
       </c>
@@ -18462,7 +18465,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C25" s="49" t="s">
         <v>308</v>
       </c>
@@ -18477,7 +18480,7 @@
       </c>
       <c r="G25" s="49"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C26" s="49" t="s">
         <v>312</v>
       </c>
@@ -18492,75 +18495,75 @@
         <v>307</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C29" s="12" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C30" s="12" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C31" s="12" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:10" ht="13" x14ac:dyDescent="0.3">
       <c r="C33" s="16" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C34" s="12" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C35" s="12" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C36" s="12" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C37" s="12" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C38" s="12" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C39" s="12" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C40" s="12" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="41" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C41" s="12" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C42" s="49"/>
     </row>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C43" s="49" t="s">
         <v>268</v>
       </c>
@@ -18572,7 +18575,7 @@
       <c r="I43" s="49"/>
       <c r="J43" s="49"/>
     </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C44" s="49" t="s">
         <v>269</v>
       </c>
@@ -18584,7 +18587,7 @@
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
     </row>
-    <row r="45" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C45" s="49" t="s">
         <v>270</v>
       </c>
@@ -18598,7 +18601,7 @@
       <c r="I45" s="49"/>
       <c r="J45" s="49"/>
     </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C46" s="49" t="s">
         <v>271</v>
       </c>
@@ -18612,7 +18615,7 @@
       <c r="I46" s="49"/>
       <c r="J46" s="49"/>
     </row>
-    <row r="47" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C47" s="49" t="s">
         <v>272</v>
       </c>
@@ -18626,7 +18629,7 @@
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
     </row>
-    <row r="48" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C48" s="49"/>
       <c r="D48" s="49"/>
       <c r="E48" s="49"/>
@@ -18636,7 +18639,7 @@
       <c r="I48" s="49"/>
       <c r="J48" s="49"/>
     </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C49" s="49" t="s">
         <v>273</v>
       </c>
@@ -18648,7 +18651,7 @@
       <c r="I49" s="49"/>
       <c r="J49" s="49"/>
     </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C50" s="49"/>
       <c r="D50" s="49"/>
       <c r="E50" s="49"/>
@@ -18658,7 +18661,7 @@
       <c r="I50" s="49"/>
       <c r="J50" s="49"/>
     </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C51" s="49" t="s">
         <v>274</v>
       </c>
@@ -18670,7 +18673,7 @@
       <c r="I51" s="49"/>
       <c r="J51" s="49"/>
     </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C52" s="49" t="s">
         <v>275</v>
       </c>
@@ -18682,7 +18685,7 @@
       <c r="I52" s="49"/>
       <c r="J52" s="49"/>
     </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C53" s="49" t="s">
         <v>276</v>
       </c>
@@ -18694,7 +18697,7 @@
       <c r="I53" s="49"/>
       <c r="J53" s="49"/>
     </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C54" s="49" t="s">
         <v>277</v>
       </c>
@@ -18706,182 +18709,182 @@
       <c r="I54" s="49"/>
       <c r="J54" s="49"/>
     </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:10" ht="13" x14ac:dyDescent="0.3">
       <c r="C56" s="16" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C57" s="12" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="58" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C58" s="12" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="59" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C59" s="12" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C60" s="12" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C61" s="12" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="62" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C62" s="12" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="63" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C63" s="12" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C65" s="12" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C67" s="16" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C68" s="12" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C69" s="12" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C70" s="12" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C72" s="16" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C73" s="12" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C74" s="12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C75" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C76" s="12" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C78" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C79" s="12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C80" s="12" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C81" s="12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C82" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C83" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C84" s="12" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C85" s="12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C86" s="12" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C88" s="16" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C89" s="12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C91" s="16" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C94" s="16" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C95" s="12" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C98" s="16" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C99" s="54" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C101" s="16" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C102" s="54" t="s">
         <v>518</v>
       </c>
@@ -18900,34 +18903,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B2" s="31" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" s="31" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="31" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="31" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
         <v>292</v>
       </c>
@@ -18945,18 +18948,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82471C3B-949C-4752-B2F1-2746AFE88D3C}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="63" t="s">
         <v>461</v>
       </c>
@@ -18964,7 +18967,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>462</v>
       </c>
@@ -18972,7 +18975,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="63" t="s">
         <v>463</v>
       </c>
@@ -18980,7 +18983,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="63" t="s">
         <v>1</v>
       </c>
@@ -18988,13 +18991,13 @@
         <v>472</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="63"/>
       <c r="C6" s="63" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="63" t="s">
         <v>465</v>
       </c>
@@ -19002,7 +19005,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="63" t="s">
         <v>14</v>
       </c>
@@ -19010,43 +19013,43 @@
         <v>473</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="63" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="B10" s="63"/>
       <c r="C10" s="64" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" s="63" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C13" s="64" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C14" s="63" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C16" s="64" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C18" s="64" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C20" s="64" t="s">
         <v>568</v>
       </c>
@@ -19062,18 +19065,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>10</v>
       </c>
@@ -19081,7 +19084,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>21</v>
       </c>
@@ -19089,7 +19092,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -19097,7 +19100,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -19105,7 +19108,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>22</v>
       </c>
@@ -19113,7 +19116,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -19121,7 +19124,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -19129,17 +19132,17 @@
         <v>345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" s="31" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" s="31" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>23</v>
       </c>
@@ -19147,37 +19150,37 @@
         <v>359</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C13" s="64" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:15" ht="13" x14ac:dyDescent="0.3">
       <c r="C17" s="64" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" ht="13" x14ac:dyDescent="0.3">
       <c r="C19" s="64" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" ht="13" x14ac:dyDescent="0.3">
       <c r="C22" s="64" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" ht="13" x14ac:dyDescent="0.3">
       <c r="C23" s="31" t="s">
         <v>340</v>
       </c>
@@ -19185,27 +19188,27 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C24" s="31" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C25" s="31" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" ht="13" x14ac:dyDescent="0.3">
       <c r="C27" s="64" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C29" s="31" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D30" s="31" t="s">
         <v>347</v>
       </c>
@@ -19219,7 +19222,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D31" s="31" t="s">
         <v>351</v>
       </c>
@@ -19233,7 +19236,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C32" s="31" t="s">
         <v>355</v>
       </c>
@@ -19250,7 +19253,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="33" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C33" s="31" t="s">
         <v>356</v>
       </c>
@@ -19267,7 +19270,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="34" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C34" s="31" t="s">
         <v>357</v>
       </c>
@@ -19284,27 +19287,27 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C36" s="31" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="38" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C38" s="31" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="39" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C39" s="31" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="40" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C40" s="31" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="41" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:15" ht="13" x14ac:dyDescent="0.3">
       <c r="C41" s="31" t="s">
         <v>209</v>
       </c>
@@ -19312,7 +19315,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="42" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C42" s="31" t="s">
         <v>210</v>
       </c>
@@ -19320,7 +19323,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="43" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C43" s="31" t="s">
         <v>211</v>
       </c>
@@ -19328,17 +19331,17 @@
         <v>136</v>
       </c>
     </row>
-    <row r="45" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:15" ht="13" x14ac:dyDescent="0.3">
       <c r="C45" s="64" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="46" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C49" s="64" t="s">
         <v>510</v>
       </c>
@@ -19355,18 +19358,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F229D7-D433-42EA-85D9-844DBCCD7DB2}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="63" t="s">
         <v>461</v>
       </c>
@@ -19374,7 +19377,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>462</v>
       </c>
@@ -19382,7 +19385,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="63" t="s">
         <v>1</v>
       </c>
@@ -19390,7 +19393,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="63" t="s">
         <v>488</v>
       </c>
@@ -19398,7 +19401,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="63" t="s">
         <v>14</v>
       </c>
@@ -19406,32 +19409,32 @@
         <v>490</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="63" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C8" s="64" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C11" s="64" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C14" s="64" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C17" s="64" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" s="63" t="s">
         <v>555</v>
       </c>
@@ -19447,19 +19450,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>52</v>
       </c>
       <c r="C1" s="31"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>10</v>
       </c>
@@ -19467,7 +19470,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -19475,7 +19478,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -19483,12 +19486,12 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C5" s="31" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>22</v>
       </c>
@@ -19496,7 +19499,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>14</v>
       </c>
@@ -19504,47 +19507,47 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="31"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="31"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C10" s="64" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" s="63" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" s="31"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C13" s="64" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C14" s="31" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C15" s="31" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C16" s="31" t="s">
         <v>325</v>
       </c>
@@ -19561,18 +19564,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C21B209-A8FB-4E3C-93A8-FCECAB25B921}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="63" t="s">
         <v>461</v>
       </c>
@@ -19580,7 +19583,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>462</v>
       </c>
@@ -19588,7 +19591,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="63" t="s">
         <v>1</v>
       </c>
@@ -19596,7 +19599,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="63" t="s">
         <v>488</v>
       </c>
@@ -19604,7 +19607,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="63" t="s">
         <v>465</v>
       </c>
@@ -19612,27 +19615,27 @@
         <v>544</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="63" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C8" s="64" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C10" s="64" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C12" s="64" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C14" s="64" t="s">
         <v>551</v>
       </c>
@@ -19646,9 +19649,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19766,19 +19772,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E96F600B-2292-4B54-9B9B-0627F8C06A82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25317B7F-B4C1-44E7-BEEE-569C53B5B056}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19800,9 +19802,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25317B7F-B4C1-44E7-BEEE-569C53B5B056}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E96F600B-2292-4B54-9B9B-0627F8C06A82}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>